--- a/output/final/geo/geo distributors (status checked)/geo_ag_drone_verified_distributors.xlsx
+++ b/output/final/geo/geo distributors (status checked)/geo_ag_drone_verified_distributors.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$5:$U$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$5:$U$174</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Companies'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U175"/>
+  <dimension ref="A1:U174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -647,7 +647,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Distributors listed: 170     |     Headquarter countries: 1     |     Acquired by another group (named in the company name): 0</t>
+          <t>Distributors listed: 169     |     Headquarter countries: 1     |     Acquired by another group (named in the company name): 0</t>
         </is>
       </c>
     </row>
@@ -8342,16 +8342,16 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>Gurudrone Agritech Pvt Ltd</t>
+          <t>Agro Power Hi-Tech Solution</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
         <is>
-          <t>gurudrone.com</t>
+          <t>agropowerhitechsolution.com</t>
         </is>
       </c>
       <c r="D96" s="11" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
@@ -8375,22 +8375,22 @@
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>5-20</t>
         </is>
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drone components; fertilizer spreading kits; nozzles</t>
+          <t>Pesticide pressure pumps; drone-mounted sprayers; agriculture components</t>
         </is>
       </c>
       <c r="K96" s="14" t="inlineStr">
         <is>
-          <t>Distribution of custom mechanical frames, carbon fiber limbs, and distribution systems for farming copters.</t>
+          <t>Supplying flow-control systems and electronic replacement equipment for automated chemical applications.</t>
         </is>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>Centrifugal atomizing nozzles; agricultural drone telemetry systems; landing gears</t>
+          <t>High-pressure diaphragm pumps; crop-sprayer nozzles; pressure line manifolds</t>
         </is>
       </c>
       <c r="M96" s="11" t="inlineStr">
@@ -8402,10 +8402,14 @@
       <c r="O96" s="14" t="inlineStr"/>
       <c r="P96" s="14" t="inlineStr"/>
       <c r="Q96" s="14" t="inlineStr"/>
-      <c r="R96" s="14" t="inlineStr"/>
+      <c r="R96" s="14" t="inlineStr">
+        <is>
+          <t>+919787966615</t>
+        </is>
+      </c>
       <c r="S96" s="13" t="inlineStr">
         <is>
-          <t>gurudrone.com</t>
+          <t>agropowerhitechsolution.com</t>
         </is>
       </c>
       <c r="T96" s="14" t="inlineStr"/>
@@ -8421,20 +8425,20 @@
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>Agro Power Hi-Tech Solution</t>
+          <t>Phoenix UAV &amp; drones</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>agropowerhitechsolution.com</t>
+          <t>flowerdroppingdrone.com</t>
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="E97" s="18" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="F97" s="18" t="inlineStr">
@@ -8454,27 +8458,27 @@
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
-          <t>5-20</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J97" s="18" t="inlineStr">
         <is>
-          <t>Pesticide pressure pumps; drone-mounted sprayers; agriculture components</t>
+          <t>Precision crop scouting drones; payload attachments; multi-spectral sensors</t>
         </is>
       </c>
       <c r="K97" s="18" t="inlineStr">
         <is>
-          <t>Supplying flow-control systems and electronic replacement equipment for automated chemical applications.</t>
+          <t>Distribution of certified commercial aerial platforms and professional hardware troubleshooting.</t>
         </is>
       </c>
       <c r="L97" s="18" t="inlineStr">
         <is>
-          <t>High-pressure diaphragm pumps; crop-sprayer nozzles; pressure line manifolds</t>
+          <t>DJI Agras hardware, DJI Mavic series, aerial payload mechanisms</t>
         </is>
       </c>
       <c r="M97" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N97" s="18" t="inlineStr"/>
@@ -8483,12 +8487,12 @@
       <c r="Q97" s="18" t="inlineStr"/>
       <c r="R97" s="18" t="inlineStr">
         <is>
-          <t>+919787966615</t>
+          <t>+91 80007 55781</t>
         </is>
       </c>
       <c r="S97" s="17" t="inlineStr">
         <is>
-          <t>agropowerhitechsolution.com</t>
+          <t>flowerdroppingdrone.com</t>
         </is>
       </c>
       <c r="T97" s="18" t="inlineStr"/>
@@ -8504,20 +8508,20 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>Phoenix UAV &amp; drones</t>
+          <t>Rcproduct.in</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
         <is>
-          <t>flowerdroppingdrone.com</t>
+          <t>rcproduct.in</t>
         </is>
       </c>
       <c r="D98" s="11" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Vadodara, India</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
@@ -8542,17 +8546,17 @@
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>Precision crop scouting drones; payload attachments; multi-spectral sensors</t>
+          <t>Agriculture flight controllers; FPV propulsion systems; remote management hardware</t>
         </is>
       </c>
       <c r="K98" s="14" t="inlineStr">
         <is>
-          <t>Distribution of certified commercial aerial platforms and professional hardware troubleshooting.</t>
+          <t>Distribution of specialist components, sub-systems, and precision controllers for agricultural applications.</t>
         </is>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>DJI Agras hardware, DJI Mavic series, aerial payload mechanisms</t>
+          <t>DJI N3-AG Agriculture Flight Controller, multi-rotor telemetry modules</t>
         </is>
       </c>
       <c r="M98" s="11" t="inlineStr">
@@ -8564,14 +8568,10 @@
       <c r="O98" s="14" t="inlineStr"/>
       <c r="P98" s="14" t="inlineStr"/>
       <c r="Q98" s="14" t="inlineStr"/>
-      <c r="R98" s="14" t="inlineStr">
-        <is>
-          <t>+91 80007 55781</t>
-        </is>
-      </c>
+      <c r="R98" s="14" t="inlineStr"/>
       <c r="S98" s="13" t="inlineStr">
         <is>
-          <t>flowerdroppingdrone.com</t>
+          <t>rcproduct.in</t>
         </is>
       </c>
       <c r="T98" s="14" t="inlineStr"/>
@@ -8587,16 +8587,16 @@
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>Rcproduct.in</t>
+          <t>Drone bazaar</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>rcproduct.in</t>
+          <t>drone-bazaar.ueniweb.com</t>
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="E99" s="18" t="inlineStr">
         <is>
@@ -8625,17 +8625,17 @@
       </c>
       <c r="J99" s="18" t="inlineStr">
         <is>
-          <t>Agriculture flight controllers; FPV propulsion systems; remote management hardware</t>
+          <t>Commercial drone systems; drone sub-assemblies; aerial surveying sensors</t>
         </is>
       </c>
       <c r="K99" s="18" t="inlineStr">
         <is>
-          <t>Distribution of specialist components, sub-systems, and precision controllers for agricultural applications.</t>
+          <t>Sourcing and distribution of multi-rotor platforms and tailored accessories for modern enterprise applications.</t>
         </is>
       </c>
       <c r="L99" s="18" t="inlineStr">
         <is>
-          <t>DJI N3-AG Agriculture Flight Controller, multi-rotor telemetry modules</t>
+          <t>Enterprise crop monitoring drones, drone power modules</t>
         </is>
       </c>
       <c r="M99" s="15" t="inlineStr">
@@ -8647,13 +8647,21 @@
       <c r="O99" s="18" t="inlineStr"/>
       <c r="P99" s="18" t="inlineStr"/>
       <c r="Q99" s="18" t="inlineStr"/>
-      <c r="R99" s="18" t="inlineStr"/>
+      <c r="R99" s="18" t="inlineStr">
+        <is>
+          <t>094290 61432</t>
+        </is>
+      </c>
       <c r="S99" s="17" t="inlineStr">
         <is>
-          <t>rcproduct.in</t>
-        </is>
-      </c>
-      <c r="T99" s="18" t="inlineStr"/>
+          <t>drone-bazaar.ueniweb.com</t>
+        </is>
+      </c>
+      <c r="T99" s="17" t="inlineStr">
+        <is>
+          <t>parthzaveri265@gmail.com</t>
+        </is>
+      </c>
       <c r="U99" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -8666,20 +8674,20 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>Drone bazaar</t>
+          <t>Alicorn Aviation Pvt Ltd</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>drone-bazaar.ueniweb.com</t>
+          <t>alicornaviation.com</t>
         </is>
       </c>
       <c r="D100" s="11" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Vadodara, India</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
@@ -8699,22 +8707,22 @@
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>1-20</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>Commercial drone systems; drone sub-assemblies; aerial surveying sensors</t>
+          <t>Commercial drones; specialized flight electronics; aerial imaging sensors</t>
         </is>
       </c>
       <c r="K100" s="14" t="inlineStr">
         <is>
-          <t>Sourcing and distribution of multi-rotor platforms and tailored accessories for modern enterprise applications.</t>
+          <t>Reselling verifiable drone hardware and matching field automation software suites.</t>
         </is>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>Enterprise crop monitoring drones, drone power modules</t>
+          <t>Multi-rotor field surveying UAVs, agricultural payload tracking modules, and precision GPS accessories.</t>
         </is>
       </c>
       <c r="M100" s="11" t="inlineStr">
@@ -8726,21 +8734,13 @@
       <c r="O100" s="14" t="inlineStr"/>
       <c r="P100" s="14" t="inlineStr"/>
       <c r="Q100" s="14" t="inlineStr"/>
-      <c r="R100" s="14" t="inlineStr">
-        <is>
-          <t>094290 61432</t>
-        </is>
-      </c>
+      <c r="R100" s="14" t="inlineStr"/>
       <c r="S100" s="13" t="inlineStr">
         <is>
-          <t>drone-bazaar.ueniweb.com</t>
-        </is>
-      </c>
-      <c r="T100" s="13" t="inlineStr">
-        <is>
-          <t>parthzaveri265@gmail.com</t>
-        </is>
-      </c>
+          <t>alicornaviation.com</t>
+        </is>
+      </c>
+      <c r="T100" s="14" t="inlineStr"/>
       <c r="U100" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -8753,16 +8753,16 @@
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>Alicorn Aviation Pvt Ltd</t>
+          <t>Akshar Integrated Facility Services</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>alicornaviation.com</t>
+          <t>aksharonline.com</t>
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E101" s="18" t="inlineStr">
         <is>
@@ -8786,27 +8786,27 @@
       </c>
       <c r="I101" s="15" t="inlineStr">
         <is>
-          <t>1-20</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J101" s="18" t="inlineStr">
         <is>
-          <t>Commercial drones; specialized flight electronics; aerial imaging sensors</t>
+          <t>Commercial agricultural drones; digital flight telemetry equipment; aerial spray arrays</t>
         </is>
       </c>
       <c r="K101" s="18" t="inlineStr">
         <is>
-          <t>Reselling verifiable drone hardware and matching field automation software suites.</t>
+          <t>Integrating remote-piloted hardware with localized precision farming workflows.</t>
         </is>
       </c>
       <c r="L101" s="18" t="inlineStr">
         <is>
-          <t>Multi-rotor field surveying UAVs, agricultural payload tracking modules, and precision GPS accessories.</t>
+          <t>DJI 8-Axis Octocopter systems, high-definition digital crop cameras, and localized field spraying accessories.</t>
         </is>
       </c>
       <c r="M101" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N101" s="18" t="inlineStr"/>
@@ -8816,7 +8816,7 @@
       <c r="R101" s="18" t="inlineStr"/>
       <c r="S101" s="17" t="inlineStr">
         <is>
-          <t>alicornaviation.com</t>
+          <t>aksharonline.com</t>
         </is>
       </c>
       <c r="T101" s="18" t="inlineStr"/>
@@ -8826,22 +8826,22 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="46.5" customHeight="1">
+    <row r="102" ht="33" customHeight="1">
       <c r="A102" s="11" t="n">
         <v>97</v>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>Akshar Integrated Facility Services</t>
-        </is>
-      </c>
-      <c r="C102" s="13" t="inlineStr">
-        <is>
-          <t>aksharonline.com</t>
+          <t>Jiyi Aero Green Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>u46539gj2023ptc144514</t>
         </is>
       </c>
       <c r="D102" s="11" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
@@ -8865,22 +8865,22 @@
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>Commercial agricultural drones; digital flight telemetry equipment; aerial spray arrays</t>
+          <t>Agricultural drone sprayers; precision farm machinery</t>
         </is>
       </c>
       <c r="K102" s="14" t="inlineStr">
         <is>
-          <t>Integrating remote-piloted hardware with localized precision farming workflows.</t>
+          <t>Wholesale distribution and supply of drone spray systems for agricultural fields</t>
         </is>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>DJI 8-Axis Octocopter systems, high-definition digital crop cameras, and localized field spraying accessories.</t>
+          <t>Agricultural drone sprayers, crop spraying UAV systems</t>
         </is>
       </c>
       <c r="M102" s="11" t="inlineStr">
@@ -8893,9 +8893,9 @@
       <c r="P102" s="14" t="inlineStr"/>
       <c r="Q102" s="14" t="inlineStr"/>
       <c r="R102" s="14" t="inlineStr"/>
-      <c r="S102" s="13" t="inlineStr">
-        <is>
-          <t>aksharonline.com</t>
+      <c r="S102" s="14" t="inlineStr">
+        <is>
+          <t>u46539gj2023ptc144514</t>
         </is>
       </c>
       <c r="T102" s="14" t="inlineStr"/>
@@ -8911,16 +8911,16 @@
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>Jiyi Aero Green Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="inlineStr">
-        <is>
-          <t>u46539gj2023ptc144514</t>
+          <t>Vibrant Engineering Mechanics &amp; Automation Controls</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>vibrantengg.com</t>
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="E103" s="18" t="inlineStr">
         <is>
@@ -8944,27 +8944,27 @@
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J103" s="18" t="inlineStr">
         <is>
-          <t>Agricultural drone sprayers; precision farm machinery</t>
+          <t>Agricultural spray drones; automation control components</t>
         </is>
       </c>
       <c r="K103" s="18" t="inlineStr">
         <is>
-          <t>Wholesale distribution and supply of drone spray systems for agricultural fields</t>
+          <t>Industrial automation components and agricultural spray drone distribution</t>
         </is>
       </c>
       <c r="L103" s="18" t="inlineStr">
         <is>
-          <t>Agricultural drone sprayers, crop spraying UAV systems</t>
+          <t>10L Agriculture Spray Drone, flight automation systems</t>
         </is>
       </c>
       <c r="M103" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N103" s="18" t="inlineStr"/>
@@ -8972,9 +8972,9 @@
       <c r="P103" s="18" t="inlineStr"/>
       <c r="Q103" s="18" t="inlineStr"/>
       <c r="R103" s="18" t="inlineStr"/>
-      <c r="S103" s="18" t="inlineStr">
-        <is>
-          <t>u46539gj2023ptc144514</t>
+      <c r="S103" s="17" t="inlineStr">
+        <is>
+          <t>vibrantengg.com</t>
         </is>
       </c>
       <c r="T103" s="18" t="inlineStr"/>
@@ -8984,22 +8984,22 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="33" customHeight="1">
+    <row r="104" ht="46.5" customHeight="1">
       <c r="A104" s="11" t="n">
         <v>99</v>
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>Vibrant Engineering Mechanics &amp; Automation Controls</t>
+          <t>Hexon Enterprise</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
         <is>
-          <t>vibrantengg.com</t>
+          <t>hexonenterprise.com</t>
         </is>
       </c>
       <c r="D104" s="11" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
@@ -9023,22 +9023,22 @@
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>Agricultural spray drones; automation control components</t>
+          <t>Commercial UAVs; multispectral cameras; enterprise agricultural drone platforms</t>
         </is>
       </c>
       <c r="K104" s="14" t="inlineStr">
         <is>
-          <t>Industrial automation components and agricultural spray drone distribution</t>
+          <t>Enterprise commercial drone sales and precision agriculture spraying solutions</t>
         </is>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>10L Agriculture Spray Drone, flight automation systems</t>
+          <t>DJI Agras T50, DJI Matrice series, multispectral imaging systems</t>
         </is>
       </c>
       <c r="M104" s="11" t="inlineStr">
@@ -9053,7 +9053,7 @@
       <c r="R104" s="14" t="inlineStr"/>
       <c r="S104" s="13" t="inlineStr">
         <is>
-          <t>vibrantengg.com</t>
+          <t>hexonenterprise.com</t>
         </is>
       </c>
       <c r="T104" s="14" t="inlineStr"/>
@@ -9069,20 +9069,20 @@
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>Hexon Enterprise</t>
+          <t>Aagosh</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>hexonenterprise.com</t>
+          <t>aagosh.in</t>
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="E105" s="18" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Surat, India</t>
         </is>
       </c>
       <c r="F105" s="18" t="inlineStr">
@@ -9107,17 +9107,17 @@
       </c>
       <c r="J105" s="18" t="inlineStr">
         <is>
-          <t>Commercial UAVs; multispectral cameras; enterprise agricultural drone platforms</t>
+          <t>Heavy-lift agricultural drone frames; precision UAV spray systems; high-pressure pumps</t>
         </is>
       </c>
       <c r="K105" s="18" t="inlineStr">
         <is>
-          <t>Enterprise commercial drone sales and precision agriculture spraying solutions</t>
+          <t>Sourcing and distribution partner for specialized FPV electronics and industrial agricultural drone payloads.</t>
         </is>
       </c>
       <c r="L105" s="18" t="inlineStr">
         <is>
-          <t>DJI Agras T50, DJI Matrice series, multispectral imaging systems</t>
+          <t>EFT 6 Axis E616P spraying drone frames, specialized anti-drift nozzles, Walksnail and DJI goggles.</t>
         </is>
       </c>
       <c r="M105" s="15" t="inlineStr">
@@ -9127,15 +9127,27 @@
       </c>
       <c r="N105" s="18" t="inlineStr"/>
       <c r="O105" s="18" t="inlineStr"/>
-      <c r="P105" s="18" t="inlineStr"/>
+      <c r="P105" s="17" t="inlineStr">
+        <is>
+          <t>sales@aagosh.in</t>
+        </is>
+      </c>
       <c r="Q105" s="18" t="inlineStr"/>
-      <c r="R105" s="18" t="inlineStr"/>
+      <c r="R105" s="18" t="inlineStr">
+        <is>
+          <t>+917016794172</t>
+        </is>
+      </c>
       <c r="S105" s="17" t="inlineStr">
         <is>
-          <t>hexonenterprise.com</t>
-        </is>
-      </c>
-      <c r="T105" s="18" t="inlineStr"/>
+          <t>aagosh.in</t>
+        </is>
+      </c>
+      <c r="T105" s="17" t="inlineStr">
+        <is>
+          <t>sales@aagosh.in</t>
+        </is>
+      </c>
       <c r="U105" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -9148,20 +9160,20 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>Aagosh</t>
+          <t>Drone Planet</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>aagosh.in</t>
+          <t>droneplanet.in</t>
         </is>
       </c>
       <c r="D106" s="11" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>Surat, India</t>
+          <t>Gurugram, India</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -9181,22 +9193,22 @@
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>Heavy-lift agricultural drone frames; precision UAV spray systems; high-pressure pumps</t>
+          <t>Agricultural multi-rotors; replacement drone spares; payload sensors</t>
         </is>
       </c>
       <c r="K106" s="14" t="inlineStr">
         <is>
-          <t>Sourcing and distribution partner for specialized FPV electronics and industrial agricultural drone payloads.</t>
+          <t>Commercial drone marketplace supplying remote pilots and enterprise groups with verified precision equipment.</t>
         </is>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>EFT 6 Axis E616P spraying drone frames, specialized anti-drift nozzles, Walksnail and DJI goggles.</t>
+          <t>Agricultural spraying frames, replacement drone batteries, custom avionics accessories</t>
         </is>
       </c>
       <c r="M106" s="11" t="inlineStr">
@@ -9208,23 +9220,23 @@
       <c r="O106" s="14" t="inlineStr"/>
       <c r="P106" s="13" t="inlineStr">
         <is>
-          <t>sales@aagosh.in</t>
+          <t>sales@droneplanet.in</t>
         </is>
       </c>
       <c r="Q106" s="14" t="inlineStr"/>
       <c r="R106" s="14" t="inlineStr">
         <is>
-          <t>+917016794172</t>
+          <t>+91 97735 71992</t>
         </is>
       </c>
       <c r="S106" s="13" t="inlineStr">
         <is>
-          <t>aagosh.in</t>
+          <t>droneplanet.in</t>
         </is>
       </c>
       <c r="T106" s="13" t="inlineStr">
         <is>
-          <t>sales@aagosh.in</t>
+          <t>support@droneplanet.in</t>
         </is>
       </c>
       <c r="U106" s="11" t="inlineStr">
@@ -9239,20 +9251,20 @@
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>Drone Planet</t>
+          <t>Airone</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>droneplanet.in</t>
+          <t>aironeventures.com</t>
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="E107" s="18" t="inlineStr">
         <is>
-          <t>Gurugram, India</t>
+          <t>Howrah, India</t>
         </is>
       </c>
       <c r="F107" s="18" t="inlineStr">
@@ -9272,22 +9284,22 @@
       </c>
       <c r="I107" s="15" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J107" s="18" t="inlineStr">
         <is>
-          <t>Agricultural multi-rotors; replacement drone spares; payload sensors</t>
+          <t>Agricultural unmanned aerial vehicles; high-capacity drone batteries</t>
         </is>
       </c>
       <c r="K107" s="18" t="inlineStr">
         <is>
-          <t>Commercial drone marketplace supplying remote pilots and enterprise groups with verified precision equipment.</t>
+          <t>Drone supply chain, after-sales technical maintenance, and industrial unmanned aviation solutions</t>
         </is>
       </c>
       <c r="L107" s="18" t="inlineStr">
         <is>
-          <t>Agricultural spraying frames, replacement drone batteries, custom avionics accessories</t>
+          <t>DJI Agras T50, DJI Agras T10, EFT E416P</t>
         </is>
       </c>
       <c r="M107" s="15" t="inlineStr">
@@ -9295,29 +9307,29 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N107" s="18" t="inlineStr"/>
-      <c r="O107" s="18" t="inlineStr"/>
-      <c r="P107" s="17" t="inlineStr">
-        <is>
-          <t>sales@droneplanet.in</t>
-        </is>
-      </c>
+      <c r="N107" s="18" t="inlineStr">
+        <is>
+          <t>Emroz Sardar</t>
+        </is>
+      </c>
+      <c r="O107" s="18" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="P107" s="18" t="inlineStr"/>
       <c r="Q107" s="18" t="inlineStr"/>
       <c r="R107" s="18" t="inlineStr">
         <is>
-          <t>+91 97735 71992</t>
+          <t>+917943440815</t>
         </is>
       </c>
       <c r="S107" s="17" t="inlineStr">
         <is>
-          <t>droneplanet.in</t>
-        </is>
-      </c>
-      <c r="T107" s="17" t="inlineStr">
-        <is>
-          <t>support@droneplanet.in</t>
-        </is>
-      </c>
+          <t>aironeventures.com</t>
+        </is>
+      </c>
+      <c r="T107" s="18" t="inlineStr"/>
       <c r="U107" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -9330,20 +9342,20 @@
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>Airone</t>
+          <t>a2zRC</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>aironeventures.com</t>
+          <t>a2zrc.com</t>
         </is>
       </c>
       <c r="D108" s="11" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Howrah, India</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -9363,22 +9375,22 @@
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>Agricultural unmanned aerial vehicles; high-capacity drone batteries</t>
+          <t>Agricultural spraying drones; heavy lift multirotors; flight controllers; tracking software</t>
         </is>
       </c>
       <c r="K108" s="14" t="inlineStr">
         <is>
-          <t>Drone supply chain, after-sales technical maintenance, and industrial unmanned aviation solutions</t>
+          <t>E-commerce supply and distribution of commercial drone assemblies and components</t>
         </is>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>DJI Agras T50, DJI Agras T10, EFT E416P</t>
+          <t>16 Litre Hexacopter Agricultural Spraying Drone, 10 Litre Agricultural Spraying Drone</t>
         </is>
       </c>
       <c r="M108" s="11" t="inlineStr">
@@ -9386,29 +9398,25 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N108" s="14" t="inlineStr">
-        <is>
-          <t>Emroz Sardar</t>
-        </is>
-      </c>
-      <c r="O108" s="14" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
+      <c r="N108" s="14" t="inlineStr"/>
+      <c r="O108" s="14" t="inlineStr"/>
       <c r="P108" s="14" t="inlineStr"/>
       <c r="Q108" s="14" t="inlineStr"/>
       <c r="R108" s="14" t="inlineStr">
         <is>
-          <t>+917943440815</t>
+          <t>+916900764535</t>
         </is>
       </c>
       <c r="S108" s="13" t="inlineStr">
         <is>
-          <t>aironeventures.com</t>
-        </is>
-      </c>
-      <c r="T108" s="14" t="inlineStr"/>
+          <t>a2zrc.com</t>
+        </is>
+      </c>
+      <c r="T108" s="13" t="inlineStr">
+        <is>
+          <t>contact@a2zrc.com</t>
+        </is>
+      </c>
       <c r="U108" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -9421,16 +9429,16 @@
       </c>
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>a2zRC</t>
+          <t>PixrootKart</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>a2zrc.com</t>
+          <t>pixrootkart.com</t>
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="E109" s="18" t="inlineStr">
         <is>
@@ -9459,17 +9467,17 @@
       </c>
       <c r="J109" s="18" t="inlineStr">
         <is>
-          <t>Agricultural spraying drones; heavy lift multirotors; flight controllers; tracking software</t>
+          <t>Commercial camera drones; agricultural spraying UAVs; flight components; propulsion kits</t>
         </is>
       </c>
       <c r="K109" s="18" t="inlineStr">
         <is>
-          <t>E-commerce supply and distribution of commercial drone assemblies and components</t>
+          <t>Online retail distribution of consumer and commercial drones with localized logistics support</t>
         </is>
       </c>
       <c r="L109" s="18" t="inlineStr">
         <is>
-          <t>16 Litre Hexacopter Agricultural Spraying Drone, 10 Litre Agricultural Spraying Drone</t>
+          <t>DJI Flycart 30, precision crop-spraying drones, drone flight stabilization systems</t>
         </is>
       </c>
       <c r="M109" s="15" t="inlineStr">
@@ -9479,21 +9487,25 @@
       </c>
       <c r="N109" s="18" t="inlineStr"/>
       <c r="O109" s="18" t="inlineStr"/>
-      <c r="P109" s="18" t="inlineStr"/>
+      <c r="P109" s="17" t="inlineStr">
+        <is>
+          <t>contact@pixrootkart.com</t>
+        </is>
+      </c>
       <c r="Q109" s="18" t="inlineStr"/>
       <c r="R109" s="18" t="inlineStr">
         <is>
-          <t>+916900764535</t>
+          <t>+91 62906 84263</t>
         </is>
       </c>
       <c r="S109" s="17" t="inlineStr">
         <is>
-          <t>a2zrc.com</t>
+          <t>pixrootkart.com</t>
         </is>
       </c>
       <c r="T109" s="17" t="inlineStr">
         <is>
-          <t>contact@a2zrc.com</t>
+          <t>contact@pixrootkart.com</t>
         </is>
       </c>
       <c r="U109" s="15" t="inlineStr">
@@ -9508,16 +9520,16 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>PixrootKart</t>
+          <t>ANISH ENTERPRISES</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>pixrootkart.com</t>
+          <t>anishenterprises.com</t>
         </is>
       </c>
       <c r="D110" s="11" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
@@ -9536,27 +9548,27 @@
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Family-Owned</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>Commercial camera drones; agricultural spraying UAVs; flight components; propulsion kits</t>
+          <t>Commercial drone gimbals; drone camera accessories; handheld stabilizers</t>
         </is>
       </c>
       <c r="K110" s="14" t="inlineStr">
         <is>
-          <t>Online retail distribution of consumer and commercial drones with localized logistics support</t>
+          <t>Brick-and-mortar technology retail distribution specializing in original drone hardware and photography gear</t>
         </is>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>DJI Flycart 30, precision crop-spraying drones, drone flight stabilization systems</t>
+          <t>DJI drone hardware accessories, aerial imaging optical gimbals, replacement parts</t>
         </is>
       </c>
       <c r="M110" s="11" t="inlineStr">
@@ -9566,27 +9578,19 @@
       </c>
       <c r="N110" s="14" t="inlineStr"/>
       <c r="O110" s="14" t="inlineStr"/>
-      <c r="P110" s="13" t="inlineStr">
-        <is>
-          <t>contact@pixrootkart.com</t>
-        </is>
-      </c>
+      <c r="P110" s="14" t="inlineStr"/>
       <c r="Q110" s="14" t="inlineStr"/>
       <c r="R110" s="14" t="inlineStr">
         <is>
-          <t>+91 62906 84263</t>
+          <t>+91 89106 74706</t>
         </is>
       </c>
       <c r="S110" s="13" t="inlineStr">
         <is>
-          <t>pixrootkart.com</t>
-        </is>
-      </c>
-      <c r="T110" s="13" t="inlineStr">
-        <is>
-          <t>contact@pixrootkart.com</t>
-        </is>
-      </c>
+          <t>anishenterprises.com</t>
+        </is>
+      </c>
+      <c r="T110" s="14" t="inlineStr"/>
       <c r="U110" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -9599,20 +9603,20 @@
       </c>
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>ANISH ENTERPRISES</t>
+          <t>Xrobofly</t>
         </is>
       </c>
       <c r="C111" s="17" t="inlineStr">
         <is>
-          <t>anishenterprises.com</t>
+          <t>xrobofly.com</t>
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="E111" s="18" t="inlineStr">
         <is>
-          <t>Kolkata, India</t>
+          <t>Barrackpore, India</t>
         </is>
       </c>
       <c r="F111" s="18" t="inlineStr">
@@ -9627,27 +9631,27 @@
       </c>
       <c r="H111" s="18" t="inlineStr">
         <is>
-          <t>Family-Owned</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I111" s="15" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J111" s="18" t="inlineStr">
         <is>
-          <t>Commercial drone gimbals; drone camera accessories; handheld stabilizers</t>
+          <t>Enterprise drones; multi-rotor components; telemetry hardware; unmanned power systems</t>
         </is>
       </c>
       <c r="K111" s="18" t="inlineStr">
         <is>
-          <t>Brick-and-mortar technology retail distribution specializing in original drone hardware and photography gear</t>
+          <t>Commercial procurement and retail distribution of FPV systems and enterprise drone equipment platforms.</t>
         </is>
       </c>
       <c r="L111" s="18" t="inlineStr">
         <is>
-          <t>DJI drone hardware accessories, aerial imaging optical gimbals, replacement parts</t>
+          <t>DJI commercial drone options, telemetry components, custom power distribution modules, payload gear.</t>
         </is>
       </c>
       <c r="M111" s="15" t="inlineStr">
@@ -9661,12 +9665,12 @@
       <c r="Q111" s="18" t="inlineStr"/>
       <c r="R111" s="18" t="inlineStr">
         <is>
-          <t>+91 89106 74706</t>
+          <t>+91 62912 15916</t>
         </is>
       </c>
       <c r="S111" s="17" t="inlineStr">
         <is>
-          <t>anishenterprises.com</t>
+          <t>xrobofly.com</t>
         </is>
       </c>
       <c r="T111" s="18" t="inlineStr"/>
@@ -9676,26 +9680,26 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="46.5" customHeight="1">
+    <row r="112" ht="33" customHeight="1">
       <c r="A112" s="11" t="n">
         <v>107</v>
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>Xrobofly</t>
+          <t>Shri Agrotech Machinery</t>
         </is>
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>xrobofly.com</t>
+          <t>http://shriagrotechmachinery.in</t>
         </is>
       </c>
       <c r="D112" s="11" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>Barrackpore, India</t>
+          <t>Siliguri, India</t>
         </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
@@ -9715,27 +9719,27 @@
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>5-20</t>
         </is>
       </c>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>Enterprise drones; multi-rotor components; telemetry hardware; unmanned power systems</t>
+          <t>Agricultural mechanical implements; electronic power weeders; generators</t>
         </is>
       </c>
       <c r="K112" s="14" t="inlineStr">
         <is>
-          <t>Commercial procurement and retail distribution of FPV systems and enterprise drone equipment platforms.</t>
+          <t>B2B distribution of farm management infrastructure and precision tools</t>
         </is>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>DJI commercial drone options, telemetry components, custom power distribution modules, payload gear.</t>
+          <t>GE Power Weeders, multi-crop mechanical sprayers, automated farm machinery</t>
         </is>
       </c>
       <c r="M112" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N112" s="14" t="inlineStr"/>
@@ -9744,12 +9748,12 @@
       <c r="Q112" s="14" t="inlineStr"/>
       <c r="R112" s="14" t="inlineStr">
         <is>
-          <t>+91 62912 15916</t>
+          <t>+91 97492 50548</t>
         </is>
       </c>
       <c r="S112" s="13" t="inlineStr">
         <is>
-          <t>xrobofly.com</t>
+          <t>http://shriagrotechmachinery.in</t>
         </is>
       </c>
       <c r="T112" s="14" t="inlineStr"/>
@@ -9759,26 +9763,26 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="33" customHeight="1">
+    <row r="113" ht="46.5" customHeight="1">
       <c r="A113" s="15" t="n">
         <v>108</v>
       </c>
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>Shri Agrotech Machinery</t>
+          <t>Airpix Studios</t>
         </is>
       </c>
       <c r="C113" s="17" t="inlineStr">
         <is>
-          <t>http://shriagrotechmachinery.in</t>
+          <t>airpixstore.com</t>
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E113" s="18" t="inlineStr">
         <is>
-          <t>Siliguri, India</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="F113" s="18" t="inlineStr">
@@ -9798,27 +9802,27 @@
       </c>
       <c r="I113" s="15" t="inlineStr">
         <is>
-          <t>5-20</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J113" s="18" t="inlineStr">
         <is>
-          <t>Agricultural mechanical implements; electronic power weeders; generators</t>
+          <t>Commercial drones; thermal sensors; multispectral cameras; drone payload components</t>
         </is>
       </c>
       <c r="K113" s="18" t="inlineStr">
         <is>
-          <t>B2B distribution of farm management infrastructure and precision tools</t>
+          <t>Authorized sales, specialized testing calibration, technical repairs, and hardware support for unmanned aerial systems.</t>
         </is>
       </c>
       <c r="L113" s="18" t="inlineStr">
         <is>
-          <t>GE Power Weeders, multi-crop mechanical sprayers, automated farm machinery</t>
+          <t>DJI Matrice series enterprise drones, DJI Mavic enterprise, high-resolution cameras, thermal imagers, multi-spectral sensors</t>
         </is>
       </c>
       <c r="M113" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N113" s="18" t="inlineStr"/>
@@ -9827,15 +9831,19 @@
       <c r="Q113" s="18" t="inlineStr"/>
       <c r="R113" s="18" t="inlineStr">
         <is>
-          <t>+91 97492 50548</t>
+          <t>+91 90747 28363</t>
         </is>
       </c>
       <c r="S113" s="17" t="inlineStr">
         <is>
-          <t>http://shriagrotechmachinery.in</t>
-        </is>
-      </c>
-      <c r="T113" s="18" t="inlineStr"/>
+          <t>airpixstore.com</t>
+        </is>
+      </c>
+      <c r="T113" s="17" t="inlineStr">
+        <is>
+          <t>support@airpixstore.com</t>
+        </is>
+      </c>
       <c r="U113" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -9848,20 +9856,20 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>Airpix Studios</t>
+          <t>Asia Drone Store</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>airpixstore.com</t>
+          <t>asiadronestore.com</t>
         </is>
       </c>
       <c r="D114" s="11" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Thiruvananthapuram, India</t>
         </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
@@ -9886,17 +9894,17 @@
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>Commercial drones; thermal sensors; multispectral cameras; drone payload components</t>
+          <t>Agricultural spraying UAVs; consumer drones; drone accessories</t>
         </is>
       </c>
       <c r="K114" s="14" t="inlineStr">
         <is>
-          <t>Authorized sales, specialized testing calibration, technical repairs, and hardware support for unmanned aerial systems.</t>
+          <t>E-commerce supply, retail distribution, and technical repair services of commercial unmanned aerial vehicles.</t>
         </is>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>DJI Matrice series enterprise drones, DJI Mavic enterprise, high-resolution cameras, thermal imagers, multi-spectral sensors</t>
+          <t>DJI Agras series, drone batteries, remote controllers, and aerial spare parts.</t>
         </is>
       </c>
       <c r="M114" s="11" t="inlineStr">
@@ -9908,21 +9916,13 @@
       <c r="O114" s="14" t="inlineStr"/>
       <c r="P114" s="14" t="inlineStr"/>
       <c r="Q114" s="14" t="inlineStr"/>
-      <c r="R114" s="14" t="inlineStr">
-        <is>
-          <t>+91 90747 28363</t>
-        </is>
-      </c>
+      <c r="R114" s="14" t="inlineStr"/>
       <c r="S114" s="13" t="inlineStr">
         <is>
-          <t>airpixstore.com</t>
-        </is>
-      </c>
-      <c r="T114" s="13" t="inlineStr">
-        <is>
-          <t>support@airpixstore.com</t>
-        </is>
-      </c>
+          <t>asiadronestore.com</t>
+        </is>
+      </c>
+      <c r="T114" s="14" t="inlineStr"/>
       <c r="U114" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -9935,12 +9935,12 @@
       </c>
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>Asia Drone Store</t>
+          <t>Legacy Drone</t>
         </is>
       </c>
       <c r="C115" s="17" t="inlineStr">
         <is>
-          <t>asiadronestore.com</t>
+          <t>legacydrone.business.site</t>
         </is>
       </c>
       <c r="D115" s="15" t="n">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="E115" s="18" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram, India</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="F115" s="18" t="inlineStr">
@@ -9973,22 +9973,22 @@
       </c>
       <c r="J115" s="18" t="inlineStr">
         <is>
-          <t>Agricultural spraying UAVs; consumer drones; drone accessories</t>
+          <t>UAV electronic speed controllers; custom payload mounts; telemetry modules</t>
         </is>
       </c>
       <c r="K115" s="18" t="inlineStr">
         <is>
-          <t>E-commerce supply, retail distribution, and technical repair services of commercial unmanned aerial vehicles.</t>
+          <t>B2B parts sourcing, specialized flight control systems troubleshooting, and sub-component reselling.</t>
         </is>
       </c>
       <c r="L115" s="18" t="inlineStr">
         <is>
-          <t>DJI Agras series, drone batteries, remote controllers, and aerial spare parts.</t>
+          <t>Telemetry sensors, high-payload sprayer pump spares, and localized flight navigation matrices.</t>
         </is>
       </c>
       <c r="M115" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N115" s="18" t="inlineStr"/>
@@ -9998,7 +9998,7 @@
       <c r="R115" s="18" t="inlineStr"/>
       <c r="S115" s="17" t="inlineStr">
         <is>
-          <t>asiadronestore.com</t>
+          <t>legacydrone.business.site</t>
         </is>
       </c>
       <c r="T115" s="18" t="inlineStr"/>
@@ -10014,20 +10014,20 @@
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>Legacy Drone</t>
+          <t>Camera Scan</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>legacydrone.business.site</t>
+          <t>camerascan.org</t>
         </is>
       </c>
       <c r="D116" s="11" t="n">
-        <v>2021</v>
+        <v>1994</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Kottayam, India</t>
         </is>
       </c>
       <c r="F116" s="14" t="inlineStr">
@@ -10047,37 +10047,41 @@
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>UAV electronic speed controllers; custom payload mounts; telemetry modules</t>
+          <t>Aerial imaging systems; camera gimbals; multi-rotor platform accessories</t>
         </is>
       </c>
       <c r="K116" s="14" t="inlineStr">
         <is>
-          <t>B2B parts sourcing, specialized flight control systems troubleshooting, and sub-component reselling.</t>
+          <t>Retail distribution, commercial procurement, and specialized hardware repair for professional UAV imaging chains.</t>
         </is>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>Telemetry sensors, high-payload sprayer pump spares, and localized flight navigation matrices.</t>
+          <t>DJI Mavic and Matrice series, high-resolution CMOS payload sensors, smart battery packs</t>
         </is>
       </c>
       <c r="M116" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N116" s="14" t="inlineStr"/>
       <c r="O116" s="14" t="inlineStr"/>
       <c r="P116" s="14" t="inlineStr"/>
       <c r="Q116" s="14" t="inlineStr"/>
-      <c r="R116" s="14" t="inlineStr"/>
+      <c r="R116" s="14" t="inlineStr">
+        <is>
+          <t>+91 82816 80712</t>
+        </is>
+      </c>
       <c r="S116" s="13" t="inlineStr">
         <is>
-          <t>legacydrone.business.site</t>
+          <t>camerascan.org</t>
         </is>
       </c>
       <c r="T116" s="14" t="inlineStr"/>
@@ -10093,20 +10097,20 @@
       </c>
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>Camera Scan</t>
+          <t>Quadkart</t>
         </is>
       </c>
       <c r="C117" s="17" t="inlineStr">
         <is>
-          <t>camerascan.org</t>
+          <t>quadkart.in</t>
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>1994</v>
+        <v>2020</v>
       </c>
       <c r="E117" s="18" t="inlineStr">
         <is>
-          <t>Kottayam, India</t>
+          <t>Muvattupuzha, India</t>
         </is>
       </c>
       <c r="F117" s="18" t="inlineStr">
@@ -10126,22 +10130,22 @@
       </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J117" s="18" t="inlineStr">
         <is>
-          <t>Aerial imaging systems; camera gimbals; multi-rotor platform accessories</t>
+          <t>UAV frames; brushless motors; digital telemetry systems; speed controllers</t>
         </is>
       </c>
       <c r="K117" s="18" t="inlineStr">
         <is>
-          <t>Retail distribution, commercial procurement, and specialized hardware repair for professional UAV imaging chains.</t>
+          <t>Specialized procurement, expert assembly assistance, and components sourcing for high-performance drone platforms.</t>
         </is>
       </c>
       <c r="L117" s="18" t="inlineStr">
         <is>
-          <t>DJI Mavic and Matrice series, high-resolution CMOS payload sensors, smart battery packs</t>
+          <t>Brushless multi-rotor propulsion kits, carbon fiber component chassis, long-range telemetry kits</t>
         </is>
       </c>
       <c r="M117" s="15" t="inlineStr">
@@ -10155,12 +10159,12 @@
       <c r="Q117" s="18" t="inlineStr"/>
       <c r="R117" s="18" t="inlineStr">
         <is>
-          <t>+91 82816 80712</t>
+          <t>+91 82812 05193</t>
         </is>
       </c>
       <c r="S117" s="17" t="inlineStr">
         <is>
-          <t>camerascan.org</t>
+          <t>quadkart.in</t>
         </is>
       </c>
       <c r="T117" s="18" t="inlineStr"/>
@@ -10176,20 +10180,20 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>Quadkart</t>
+          <t>VIDEOLINKS</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>quadkart.in</t>
+          <t>videolinks.com</t>
         </is>
       </c>
       <c r="D118" s="11" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>Muvattupuzha, India</t>
+          <t>Kasaragod, India</t>
         </is>
       </c>
       <c r="F118" s="14" t="inlineStr">
@@ -10214,17 +10218,17 @@
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>UAV frames; brushless motors; digital telemetry systems; speed controllers</t>
+          <t>Cinematic and mapping drones; professional field optics; stabilizing gimbals</t>
         </is>
       </c>
       <c r="K118" s="14" t="inlineStr">
         <is>
-          <t>Specialized procurement, expert assembly assistance, and components sourcing for high-performance drone platforms.</t>
+          <t>Commercial supply lines, payload customization bundles, and expert cinematic imaging system distribution.</t>
         </is>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>Brushless multi-rotor propulsion kits, carbon fiber component chassis, long-range telemetry kits</t>
+          <t>DJI Mavic Mini and Inspire setups, neutral density lens matrix filters, high-capacity flight batteries</t>
         </is>
       </c>
       <c r="M118" s="11" t="inlineStr">
@@ -10236,14 +10240,10 @@
       <c r="O118" s="14" t="inlineStr"/>
       <c r="P118" s="14" t="inlineStr"/>
       <c r="Q118" s="14" t="inlineStr"/>
-      <c r="R118" s="14" t="inlineStr">
-        <is>
-          <t>+91 82812 05193</t>
-        </is>
-      </c>
+      <c r="R118" s="14" t="inlineStr"/>
       <c r="S118" s="13" t="inlineStr">
         <is>
-          <t>quadkart.in</t>
+          <t>videolinks.com</t>
         </is>
       </c>
       <c r="T118" s="14" t="inlineStr"/>
@@ -10259,20 +10259,20 @@
       </c>
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>VIDEOLINKS</t>
+          <t>Triumph Edge Innovation Private Limited</t>
         </is>
       </c>
       <c r="C119" s="17" t="inlineStr">
         <is>
-          <t>videolinks.com</t>
+          <t>prabhathtrades.com</t>
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="E119" s="18" t="inlineStr">
         <is>
-          <t>Kasaragod, India</t>
+          <t>Kottayam, India</t>
         </is>
       </c>
       <c r="F119" s="18" t="inlineStr">
@@ -10297,17 +10297,17 @@
       </c>
       <c r="J119" s="18" t="inlineStr">
         <is>
-          <t>Cinematic and mapping drones; professional field optics; stabilizing gimbals</t>
+          <t>Agricultural spraying drones; Seeding drones; Crop health mapping systems</t>
         </is>
       </c>
       <c r="K119" s="18" t="inlineStr">
         <is>
-          <t>Commercial supply lines, payload customization bundles, and expert cinematic imaging system distribution.</t>
+          <t>Tech-driven agricultural machinery trading and drone-based precision farming support.</t>
         </is>
       </c>
       <c r="L119" s="18" t="inlineStr">
         <is>
-          <t>DJI Mavic Mini and Inspire setups, neutral density lens matrix filters, high-capacity flight batteries</t>
+          <t>Marut Agriculture Drone AG365S, EFT frame multi-purpose sprayers, multispectral crop health mapping software</t>
         </is>
       </c>
       <c r="M119" s="15" t="inlineStr">
@@ -10315,14 +10315,26 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N119" s="18" t="inlineStr"/>
-      <c r="O119" s="18" t="inlineStr"/>
+      <c r="N119" s="18" t="inlineStr">
+        <is>
+          <t>Thulasi Manappurath</t>
+        </is>
+      </c>
+      <c r="O119" s="18" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
       <c r="P119" s="18" t="inlineStr"/>
       <c r="Q119" s="18" t="inlineStr"/>
-      <c r="R119" s="18" t="inlineStr"/>
+      <c r="R119" s="18" t="inlineStr">
+        <is>
+          <t>+91 80477 64956</t>
+        </is>
+      </c>
       <c r="S119" s="17" t="inlineStr">
         <is>
-          <t>videolinks.com</t>
+          <t>prabhathtrades.com</t>
         </is>
       </c>
       <c r="T119" s="18" t="inlineStr"/>
@@ -10338,20 +10350,20 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>Triumph Edge Innovation Private Limited</t>
+          <t>Lotus Electronics</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>prabhathtrades.com</t>
+          <t>https://www.lotuselectronics.com</t>
         </is>
       </c>
       <c r="D120" s="11" t="n">
-        <v>2023</v>
+        <v>2000</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>Kottayam, India</t>
+          <t>Indore, India</t>
         </is>
       </c>
       <c r="F120" s="14" t="inlineStr">
@@ -10371,22 +10383,22 @@
       </c>
       <c r="I120" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>100-500</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>Agricultural spraying drones; Seeding drones; Crop health mapping systems</t>
+          <t>Consumer electronics; digital imaging solutions; commercial drone lines</t>
         </is>
       </c>
       <c r="K120" s="14" t="inlineStr">
         <is>
-          <t>Tech-driven agricultural machinery trading and drone-based precision farming support.</t>
+          <t>Omnichannel distribution of authorized commercial imaging and remote aircraft technologies</t>
         </is>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>Marut Agriculture Drone AG365S, EFT frame multi-purpose sprayers, multispectral crop health mapping software</t>
+          <t>DJI multi-rotor platforms, camera accessories, flight electronics</t>
         </is>
       </c>
       <c r="M120" s="11" t="inlineStr">
@@ -10394,26 +10406,18 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N120" s="14" t="inlineStr">
-        <is>
-          <t>Thulasi Manappurath</t>
-        </is>
-      </c>
-      <c r="O120" s="14" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
+      <c r="N120" s="14" t="inlineStr"/>
+      <c r="O120" s="14" t="inlineStr"/>
       <c r="P120" s="14" t="inlineStr"/>
       <c r="Q120" s="14" t="inlineStr"/>
       <c r="R120" s="14" t="inlineStr">
         <is>
-          <t>+91 80477 64956</t>
+          <t>7389911223</t>
         </is>
       </c>
       <c r="S120" s="13" t="inlineStr">
         <is>
-          <t>prabhathtrades.com</t>
+          <t>https://www.lotuselectronics.com</t>
         </is>
       </c>
       <c r="T120" s="14" t="inlineStr"/>
@@ -10423,26 +10427,26 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="46.5" customHeight="1">
+    <row r="121" ht="33" customHeight="1">
       <c r="A121" s="15" t="n">
         <v>116</v>
       </c>
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>Lotus Electronics</t>
+          <t>Drone Wallah</t>
         </is>
       </c>
       <c r="C121" s="17" t="inlineStr">
         <is>
-          <t>https://www.lotuselectronics.com</t>
+          <t>http://www.dronewallah.in</t>
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>2000</v>
+        <v>2022</v>
       </c>
       <c r="E121" s="18" t="inlineStr">
         <is>
-          <t>Indore, India</t>
+          <t>Bhopal, India</t>
         </is>
       </c>
       <c r="F121" s="18" t="inlineStr">
@@ -10462,22 +10466,22 @@
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
-          <t>100-500</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J121" s="18" t="inlineStr">
         <is>
-          <t>Consumer electronics; digital imaging solutions; commercial drone lines</t>
+          <t>Enterprise drones; imaging drones; flight hardware</t>
         </is>
       </c>
       <c r="K121" s="18" t="inlineStr">
         <is>
-          <t>Omnichannel distribution of authorized commercial imaging and remote aircraft technologies</t>
+          <t>Supply and operational configuration of high-end autonomous flight systems</t>
         </is>
       </c>
       <c r="L121" s="18" t="inlineStr">
         <is>
-          <t>DJI multi-rotor platforms, camera accessories, flight electronics</t>
+          <t>DJI Agras agricultural series, DJI Air and Mavic enterprise hardware</t>
         </is>
       </c>
       <c r="M121" s="15" t="inlineStr">
@@ -10491,12 +10495,12 @@
       <c r="Q121" s="18" t="inlineStr"/>
       <c r="R121" s="18" t="inlineStr">
         <is>
-          <t>7389911223</t>
+          <t>+91 79749 79606</t>
         </is>
       </c>
       <c r="S121" s="17" t="inlineStr">
         <is>
-          <t>https://www.lotuselectronics.com</t>
+          <t>http://www.dronewallah.in</t>
         </is>
       </c>
       <c r="T121" s="18" t="inlineStr"/>
@@ -10506,26 +10510,26 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="33" customHeight="1">
+    <row r="122" ht="46.5" customHeight="1">
       <c r="A122" s="11" t="n">
         <v>117</v>
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>Drone Wallah</t>
+          <t>Lakshya Aerotech</t>
         </is>
       </c>
       <c r="C122" s="13" t="inlineStr">
         <is>
-          <t>http://www.dronewallah.in</t>
+          <t>lakshyaaerotech.com</t>
         </is>
       </c>
       <c r="D122" s="11" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>Bhopal, India</t>
+          <t>Vijayawada, India</t>
         </is>
       </c>
       <c r="F122" s="14" t="inlineStr">
@@ -10550,36 +10554,32 @@
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>Enterprise drones; imaging drones; flight hardware</t>
+          <t>Agricultural spraying drones; professional aerial mapping cameras; drone spare parts</t>
         </is>
       </c>
       <c r="K122" s="14" t="inlineStr">
         <is>
-          <t>Supply and operational configuration of high-end autonomous flight systems</t>
+          <t>Commercial UAV sales, localized after-sales warranty support, and comprehensive post-purchase operator validation.</t>
         </is>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>DJI Agras agricultural series, DJI Air and Mavic enterprise hardware</t>
+          <t>Multi-rotor crop protection platforms; agricultural granular spreaders; field mapping payload integration kits</t>
         </is>
       </c>
       <c r="M122" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N122" s="14" t="inlineStr"/>
       <c r="O122" s="14" t="inlineStr"/>
       <c r="P122" s="14" t="inlineStr"/>
       <c r="Q122" s="14" t="inlineStr"/>
-      <c r="R122" s="14" t="inlineStr">
-        <is>
-          <t>+91 79749 79606</t>
-        </is>
-      </c>
+      <c r="R122" s="14" t="inlineStr"/>
       <c r="S122" s="13" t="inlineStr">
         <is>
-          <t>http://www.dronewallah.in</t>
+          <t>lakshyaaerotech.com</t>
         </is>
       </c>
       <c r="T122" s="14" t="inlineStr"/>
@@ -10595,16 +10595,16 @@
       </c>
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>Lakshya Aerotech</t>
+          <t>Sri Sri Murthy Digitals</t>
         </is>
       </c>
       <c r="C123" s="17" t="inlineStr">
         <is>
-          <t>lakshyaaerotech.com</t>
+          <t>murthydigitals.in</t>
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="E123" s="18" t="inlineStr">
         <is>
@@ -10623,42 +10623,46 @@
       </c>
       <c r="H123" s="18" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Family-Owned</t>
         </is>
       </c>
       <c r="I123" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J123" s="18" t="inlineStr">
         <is>
-          <t>Agricultural spraying drones; professional aerial mapping cameras; drone spare parts</t>
+          <t>Digital cameras; drone gimbals; professional photography gear; drone accessories</t>
         </is>
       </c>
       <c r="K123" s="18" t="inlineStr">
         <is>
-          <t>Commercial UAV sales, localized after-sales warranty support, and comprehensive post-purchase operator validation.</t>
+          <t>Comprehensive retail and wholesale of drone camera systems and gimbals</t>
         </is>
       </c>
       <c r="L123" s="18" t="inlineStr">
         <is>
-          <t>Multi-rotor crop protection platforms; agricultural granular spreaders; field mapping payload integration kits</t>
+          <t>DJI drones, DJI camera systems, gimbals, vlogging gadgets, wireless microphones</t>
         </is>
       </c>
       <c r="M123" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N123" s="18" t="inlineStr"/>
       <c r="O123" s="18" t="inlineStr"/>
       <c r="P123" s="18" t="inlineStr"/>
       <c r="Q123" s="18" t="inlineStr"/>
-      <c r="R123" s="18" t="inlineStr"/>
+      <c r="R123" s="18" t="inlineStr">
+        <is>
+          <t>08662577770</t>
+        </is>
+      </c>
       <c r="S123" s="17" t="inlineStr">
         <is>
-          <t>lakshyaaerotech.com</t>
+          <t>murthydigitals.in</t>
         </is>
       </c>
       <c r="T123" s="18" t="inlineStr"/>
@@ -10668,26 +10672,26 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="46.5" customHeight="1">
+    <row r="124" ht="60" customHeight="1">
       <c r="A124" s="11" t="n">
         <v>119</v>
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>Sri Sri Murthy Digitals</t>
+          <t>Indian Drone Farmer</t>
         </is>
       </c>
       <c r="C124" s="13" t="inlineStr">
         <is>
-          <t>murthydigitals.in</t>
+          <t>https://in.linkedin.com/in/indian-drone-farmer-66b43a301</t>
         </is>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1999</v>
+        <v>2016</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>Vijayawada, India</t>
+          <t>Kovur, India</t>
         </is>
       </c>
       <c r="F124" s="14" t="inlineStr">
@@ -10702,27 +10706,27 @@
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Family-Owned</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>Digital cameras; drone gimbals; professional photography gear; drone accessories</t>
+          <t>Agricultural drone accessories; high-capacity smart batteries; flight control modules; drone propulsion units</t>
         </is>
       </c>
       <c r="K124" s="14" t="inlineStr">
         <is>
-          <t>Comprehensive retail and wholesale of drone camera systems and gimbals</t>
+          <t>B2B supply of customized replacement spare components, electronic speed controllers, and specialized agricultural drone field training.</t>
         </is>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>DJI drones, DJI camera systems, gimbals, vlogging gadgets, wireless microphones</t>
+          <t>Turbo 14S 30000mAh LiPo Smart Batteries, drone propellers, ESCs, drone motors, integrated flight controllers</t>
         </is>
       </c>
       <c r="M124" s="11" t="inlineStr">
@@ -10736,12 +10740,12 @@
       <c r="Q124" s="14" t="inlineStr"/>
       <c r="R124" s="14" t="inlineStr">
         <is>
-          <t>08662577770</t>
+          <t>+917672002024</t>
         </is>
       </c>
       <c r="S124" s="13" t="inlineStr">
         <is>
-          <t>murthydigitals.in</t>
+          <t>https://in.linkedin.com/in/indian-drone-farmer-66b43a301</t>
         </is>
       </c>
       <c r="T124" s="14" t="inlineStr"/>
@@ -10751,26 +10755,26 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
+    <row r="125" ht="46.5" customHeight="1">
       <c r="A125" s="15" t="n">
         <v>120</v>
       </c>
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>Indian Drone Farmer</t>
+          <t>Gnananetra Industries Private Limited</t>
         </is>
       </c>
       <c r="C125" s="17" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/in/indian-drone-farmer-66b43a301</t>
+          <t>gnananetra.co.in</t>
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="E125" s="18" t="inlineStr">
         <is>
-          <t>Kovur, India</t>
+          <t>Vijayawada, India</t>
         </is>
       </c>
       <c r="F125" s="18" t="inlineStr">
@@ -10790,22 +10794,22 @@
       </c>
       <c r="I125" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J125" s="18" t="inlineStr">
         <is>
-          <t>Agricultural drone accessories; high-capacity smart batteries; flight control modules; drone propulsion units</t>
+          <t>Precision agriculture drones; commercial electronics</t>
         </is>
       </c>
       <c r="K125" s="18" t="inlineStr">
         <is>
-          <t>B2B supply of customized replacement spare components, electronic speed controllers, and specialized agricultural drone field training.</t>
+          <t>Wholesale distribution of corporate assets and smart agricultural unmanned aerial vehicles</t>
         </is>
       </c>
       <c r="L125" s="18" t="inlineStr">
         <is>
-          <t>Turbo 14S 30000mAh LiPo Smart Batteries, drone propellers, ESCs, drone motors, integrated flight controllers</t>
+          <t>Garuda Aerospace Agri Kisan Drone</t>
         </is>
       </c>
       <c r="M125" s="15" t="inlineStr">
@@ -10813,47 +10817,59 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N125" s="18" t="inlineStr"/>
-      <c r="O125" s="18" t="inlineStr"/>
+      <c r="N125" s="18" t="inlineStr">
+        <is>
+          <t>Potli Priyanka</t>
+        </is>
+      </c>
+      <c r="O125" s="18" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="P125" s="18" t="inlineStr"/>
       <c r="Q125" s="18" t="inlineStr"/>
       <c r="R125" s="18" t="inlineStr">
         <is>
-          <t>+917672002024</t>
+          <t>+91 83414 17766</t>
         </is>
       </c>
       <c r="S125" s="17" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/in/indian-drone-farmer-66b43a301</t>
-        </is>
-      </c>
-      <c r="T125" s="18" t="inlineStr"/>
+          <t>gnananetra.co.in</t>
+        </is>
+      </c>
+      <c r="T125" s="17" t="inlineStr">
+        <is>
+          <t>sales@gnananetra.com</t>
+        </is>
+      </c>
       <c r="U125" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="46.5" customHeight="1">
+    <row r="126" ht="33" customHeight="1">
       <c r="A126" s="11" t="n">
         <v>121</v>
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>Gnananetra Industries Private Limited</t>
+          <t>SVR Camera Square</t>
         </is>
       </c>
       <c r="C126" s="13" t="inlineStr">
         <is>
-          <t>gnananetra.co.in</t>
+          <t>imagesquare.in.canon</t>
         </is>
       </c>
       <c r="D126" s="11" t="n">
-        <v>2024</v>
+        <v>1989</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>Vijayawada, India</t>
+          <t>Visakhapatnam, India</t>
         </is>
       </c>
       <c r="F126" s="14" t="inlineStr">
@@ -10878,17 +10894,17 @@
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>Precision agriculture drones; commercial electronics</t>
+          <t>Consumer and enterprise drones; field monitoring cameras; visual gimbals</t>
         </is>
       </c>
       <c r="K126" s="14" t="inlineStr">
         <is>
-          <t>Wholesale distribution of corporate assets and smart agricultural unmanned aerial vehicles</t>
+          <t>Wholesale and retail supply of certified optical gear and drone tracking solutions</t>
         </is>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>Garuda Aerospace Agri Kisan Drone</t>
+          <t>DJI Matrice tracking units, high-resolution aerial cameras</t>
         </is>
       </c>
       <c r="M126" s="11" t="inlineStr">
@@ -10896,31 +10912,23 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N126" s="14" t="inlineStr">
-        <is>
-          <t>Potli Priyanka</t>
-        </is>
-      </c>
-      <c r="O126" s="14" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+      <c r="N126" s="14" t="inlineStr"/>
+      <c r="O126" s="14" t="inlineStr"/>
       <c r="P126" s="14" t="inlineStr"/>
       <c r="Q126" s="14" t="inlineStr"/>
       <c r="R126" s="14" t="inlineStr">
         <is>
-          <t>+91 83414 17766</t>
+          <t>+91 83093 75575</t>
         </is>
       </c>
       <c r="S126" s="13" t="inlineStr">
         <is>
-          <t>gnananetra.co.in</t>
+          <t>imagesquare.in.canon</t>
         </is>
       </c>
       <c r="T126" s="13" t="inlineStr">
         <is>
-          <t>sales@gnananetra.com</t>
+          <t>svrcamerasquare@gmail.com</t>
         </is>
       </c>
       <c r="U126" s="11" t="inlineStr">
@@ -10929,22 +10937,22 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="33" customHeight="1">
+    <row r="127" ht="46.5" customHeight="1">
       <c r="A127" s="15" t="n">
         <v>122</v>
       </c>
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>SVR Camera Square</t>
+          <t>Gowri Natraj Enterprises</t>
         </is>
       </c>
       <c r="C127" s="17" t="inlineStr">
         <is>
-          <t>imagesquare.in.canon</t>
+          <t>gowrinatrajenterprises.com</t>
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>1989</v>
+        <v>1997</v>
       </c>
       <c r="E127" s="18" t="inlineStr">
         <is>
@@ -10963,7 +10971,7 @@
       </c>
       <c r="H127" s="18" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Family-Owned</t>
         </is>
       </c>
       <c r="I127" s="15" t="inlineStr">
@@ -10973,17 +10981,17 @@
       </c>
       <c r="J127" s="18" t="inlineStr">
         <is>
-          <t>Consumer and enterprise drones; field monitoring cameras; visual gimbals</t>
+          <t>Commercial drones; photography gear; stabilizing stabilizers</t>
         </is>
       </c>
       <c r="K127" s="18" t="inlineStr">
         <is>
-          <t>Wholesale and retail supply of certified optical gear and drone tracking solutions</t>
+          <t>Offline retail and enterprise logistics for multi-rotor flying devices and audio equipment</t>
         </is>
       </c>
       <c r="L127" s="18" t="inlineStr">
         <is>
-          <t>DJI Matrice tracking units, high-resolution aerial cameras</t>
+          <t>DJI multi-rotor platforms, wireless field audio devices</t>
         </is>
       </c>
       <c r="M127" s="15" t="inlineStr">
@@ -10997,17 +11005,17 @@
       <c r="Q127" s="18" t="inlineStr"/>
       <c r="R127" s="18" t="inlineStr">
         <is>
-          <t>+91 83093 75575</t>
+          <t>+91 98490 46798</t>
         </is>
       </c>
       <c r="S127" s="17" t="inlineStr">
         <is>
-          <t>imagesquare.in.canon</t>
+          <t>gowrinatrajenterprises.com</t>
         </is>
       </c>
       <c r="T127" s="17" t="inlineStr">
         <is>
-          <t>svrcamerasquare@gmail.com</t>
+          <t>kishore.gowrinatraj@gmail.com</t>
         </is>
       </c>
       <c r="U127" s="15" t="inlineStr">
@@ -11016,26 +11024,26 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="46.5" customHeight="1">
+    <row r="128" ht="33" customHeight="1">
       <c r="A128" s="11" t="n">
         <v>123</v>
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>Gowri Natraj Enterprises</t>
+          <t>Revi Drone Technologies</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
         <is>
-          <t>gowrinatrajenterprises.com</t>
+          <t>revidrones.com</t>
         </is>
       </c>
       <c r="D128" s="11" t="n">
-        <v>1997</v>
+        <v>2023</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>Visakhapatnam, India</t>
+          <t>Vijayawada, India</t>
         </is>
       </c>
       <c r="F128" s="14" t="inlineStr">
@@ -11050,53 +11058,45 @@
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>Family-Owned</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>5-15</t>
         </is>
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>Commercial drones; photography gear; stabilizing stabilizers</t>
+          <t>Crop mapping hardware; multi-rotor spare components</t>
         </is>
       </c>
       <c r="K128" s="14" t="inlineStr">
         <is>
-          <t>Offline retail and enterprise logistics for multi-rotor flying devices and audio equipment</t>
+          <t>Distribution of compact surveillance and remote crop-monitoring aerial packages</t>
         </is>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>DJI multi-rotor platforms, wireless field audio devices</t>
+          <t>Multi-rotor field surveying cameras, modular drone kits</t>
         </is>
       </c>
       <c r="M128" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N128" s="14" t="inlineStr"/>
       <c r="O128" s="14" t="inlineStr"/>
       <c r="P128" s="14" t="inlineStr"/>
       <c r="Q128" s="14" t="inlineStr"/>
-      <c r="R128" s="14" t="inlineStr">
-        <is>
-          <t>+91 98490 46798</t>
-        </is>
-      </c>
+      <c r="R128" s="14" t="inlineStr"/>
       <c r="S128" s="13" t="inlineStr">
         <is>
-          <t>gowrinatrajenterprises.com</t>
-        </is>
-      </c>
-      <c r="T128" s="13" t="inlineStr">
-        <is>
-          <t>kishore.gowrinatraj@gmail.com</t>
-        </is>
-      </c>
+          <t>revidrones.com</t>
+        </is>
+      </c>
+      <c r="T128" s="14" t="inlineStr"/>
       <c r="U128" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -11109,16 +11109,16 @@
       </c>
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>Revi Drone Technologies</t>
+          <t>Sreenivasa Hovering Hawks</t>
         </is>
       </c>
       <c r="C129" s="17" t="inlineStr">
         <is>
-          <t>revidrones.com</t>
+          <t>sreenivasahoveringhawks.com</t>
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E129" s="18" t="inlineStr">
         <is>
@@ -11142,37 +11142,45 @@
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
-          <t>5-15</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J129" s="18" t="inlineStr">
         <is>
-          <t>Crop mapping hardware; multi-rotor spare components</t>
+          <t>Aerial observation drones; optical capture systems</t>
         </is>
       </c>
       <c r="K129" s="18" t="inlineStr">
         <is>
-          <t>Distribution of compact surveillance and remote crop-monitoring aerial packages</t>
+          <t>Providing long-range aerial field observation hardware assets to agricultural managers</t>
         </is>
       </c>
       <c r="L129" s="18" t="inlineStr">
         <is>
-          <t>Multi-rotor field surveying cameras, modular drone kits</t>
+          <t>4K CMOS aerial camera drones, stabilization gimbals</t>
         </is>
       </c>
       <c r="M129" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="N129" s="18" t="inlineStr"/>
-      <c r="O129" s="18" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="N129" s="18" t="inlineStr">
+        <is>
+          <t>P Pilli</t>
+        </is>
+      </c>
+      <c r="O129" s="18" t="inlineStr">
+        <is>
+          <t>Proprietor</t>
+        </is>
+      </c>
       <c r="P129" s="18" t="inlineStr"/>
       <c r="Q129" s="18" t="inlineStr"/>
       <c r="R129" s="18" t="inlineStr"/>
       <c r="S129" s="17" t="inlineStr">
         <is>
-          <t>revidrones.com</t>
+          <t>sreenivasahoveringhawks.com</t>
         </is>
       </c>
       <c r="T129" s="18" t="inlineStr"/>
@@ -11188,16 +11196,16 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>Sreenivasa Hovering Hawks</t>
+          <t>Omega Agro Agencies</t>
         </is>
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>sreenivasahoveringhawks.com</t>
+          <t>omegaagroagencies.com</t>
         </is>
       </c>
       <c r="D130" s="11" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
@@ -11221,45 +11229,41 @@
       </c>
       <c r="I130" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>Aerial observation drones; optical capture systems</t>
+          <t>Crop spraying systems; motorized weeding equipment; agricultural machinery</t>
         </is>
       </c>
       <c r="K130" s="14" t="inlineStr">
         <is>
-          <t>Providing long-range aerial field observation hardware assets to agricultural managers</t>
+          <t>Supply chain provisioning of advanced agronomy machinery and farm infrastructure kits</t>
         </is>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>4K CMOS aerial camera drones, stabilization gimbals</t>
+          <t>Precision chemical crop sprayers, motorized farm weeders</t>
         </is>
       </c>
       <c r="M130" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N130" s="14" t="inlineStr">
-        <is>
-          <t>P Pilli</t>
-        </is>
-      </c>
-      <c r="O130" s="14" t="inlineStr">
-        <is>
-          <t>Proprietor</t>
-        </is>
-      </c>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N130" s="14" t="inlineStr"/>
+      <c r="O130" s="14" t="inlineStr"/>
       <c r="P130" s="14" t="inlineStr"/>
       <c r="Q130" s="14" t="inlineStr"/>
-      <c r="R130" s="14" t="inlineStr"/>
+      <c r="R130" s="14" t="inlineStr">
+        <is>
+          <t>+91 90325 19330</t>
+        </is>
+      </c>
       <c r="S130" s="13" t="inlineStr">
         <is>
-          <t>sreenivasahoveringhawks.com</t>
+          <t>omegaagroagencies.com</t>
         </is>
       </c>
       <c r="T130" s="14" t="inlineStr"/>
@@ -11275,16 +11279,16 @@
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>Omega Agro Agencies</t>
+          <t>Raga Agro Equipments</t>
         </is>
       </c>
       <c r="C131" s="17" t="inlineStr">
         <is>
-          <t>omegaagroagencies.com</t>
+          <t>ragaagroequipments.com</t>
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="E131" s="18" t="inlineStr">
         <is>
@@ -11308,22 +11312,22 @@
       </c>
       <c r="I131" s="15" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>5-20</t>
         </is>
       </c>
       <c r="J131" s="18" t="inlineStr">
         <is>
-          <t>Crop spraying systems; motorized weeding equipment; agricultural machinery</t>
+          <t>Precision agriculture implements; crop spray systems</t>
         </is>
       </c>
       <c r="K131" s="18" t="inlineStr">
         <is>
-          <t>Supply chain provisioning of advanced agronomy machinery and farm infrastructure kits</t>
+          <t>Retailing smart localized equipment for medium-scale field management operations</t>
         </is>
       </c>
       <c r="L131" s="18" t="inlineStr">
         <is>
-          <t>Precision chemical crop sprayers, motorized farm weeders</t>
+          <t>Autonomous field chemical distribution pumps and spray kits</t>
         </is>
       </c>
       <c r="M131" s="15" t="inlineStr">
@@ -11335,14 +11339,10 @@
       <c r="O131" s="18" t="inlineStr"/>
       <c r="P131" s="18" t="inlineStr"/>
       <c r="Q131" s="18" t="inlineStr"/>
-      <c r="R131" s="18" t="inlineStr">
-        <is>
-          <t>+91 90325 19330</t>
-        </is>
-      </c>
+      <c r="R131" s="18" t="inlineStr"/>
       <c r="S131" s="17" t="inlineStr">
         <is>
-          <t>omegaagroagencies.com</t>
+          <t>ragaagroequipments.com</t>
         </is>
       </c>
       <c r="T131" s="18" t="inlineStr"/>
@@ -11352,22 +11352,22 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="33" customHeight="1">
+    <row r="132" ht="46.5" customHeight="1">
       <c r="A132" s="11" t="n">
         <v>127</v>
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t>Raga Agro Equipments</t>
+          <t>Ramcor (Agricultural Drone Division)</t>
         </is>
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>ragaagroequipments.com</t>
+          <t>https://ramcorgroup.in/</t>
         </is>
       </c>
       <c r="D132" s="11" t="n">
-        <v>2018</v>
+        <v>1960</v>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
@@ -11391,37 +11391,41 @@
       </c>
       <c r="I132" s="11" t="inlineStr">
         <is>
-          <t>5-20</t>
+          <t>50-250</t>
         </is>
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>Precision agriculture implements; crop spray systems</t>
+          <t>Agricultural spraying drones; commercial utility drones; long-lasting battery camera systems</t>
         </is>
       </c>
       <c r="K132" s="14" t="inlineStr">
         <is>
-          <t>Retailing smart localized equipment for medium-scale field management operations</t>
+          <t>Sales, distribution, and after-sales service infrastructure for commercial agricultural aircraft networks</t>
         </is>
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>Autonomous field chemical distribution pumps and spray kits</t>
+          <t>IoTechWorld Agribot MX, IoTechWorld Heavybot AG+, multi-spectral crop protection sprayers</t>
         </is>
       </c>
       <c r="M132" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N132" s="14" t="inlineStr"/>
       <c r="O132" s="14" t="inlineStr"/>
       <c r="P132" s="14" t="inlineStr"/>
       <c r="Q132" s="14" t="inlineStr"/>
-      <c r="R132" s="14" t="inlineStr"/>
+      <c r="R132" s="14" t="inlineStr">
+        <is>
+          <t>+919704444785</t>
+        </is>
+      </c>
       <c r="S132" s="13" t="inlineStr">
         <is>
-          <t>ragaagroequipments.com</t>
+          <t>https://ramcorgroup.in/</t>
         </is>
       </c>
       <c r="T132" s="14" t="inlineStr"/>
@@ -11437,20 +11441,20 @@
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>Ramcor (Agricultural Drone Division)</t>
+          <t>Vizag Aerolabs Private Limited</t>
         </is>
       </c>
       <c r="C133" s="17" t="inlineStr">
         <is>
-          <t>https://ramcorgroup.in/</t>
+          <t>https://vizagaerolabspvtltd.com/</t>
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>1960</v>
+        <v>2024</v>
       </c>
       <c r="E133" s="18" t="inlineStr">
         <is>
-          <t>Vijayawada, India</t>
+          <t>Visakhapatnam, India</t>
         </is>
       </c>
       <c r="F133" s="18" t="inlineStr">
@@ -11470,22 +11474,22 @@
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
-          <t>50-250</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J133" s="18" t="inlineStr">
         <is>
-          <t>Agricultural spraying drones; commercial utility drones; long-lasting battery camera systems</t>
+          <t>Agricultural drones; aerial surveying and mapping systems; drone repair components</t>
         </is>
       </c>
       <c r="K133" s="18" t="inlineStr">
         <is>
-          <t>Sales, distribution, and after-sales service infrastructure for commercial agricultural aircraft networks</t>
+          <t>Drone repair, mapping, and technical support for agricultural and industrial operations</t>
         </is>
       </c>
       <c r="L133" s="18" t="inlineStr">
         <is>
-          <t>IoTechWorld Agribot MX, IoTechWorld Heavybot AG+, multi-spectral crop protection sprayers</t>
+          <t>DJI Agras drones, 2D and 3D mapping integrations, multispectral data support</t>
         </is>
       </c>
       <c r="M133" s="15" t="inlineStr">
@@ -11499,12 +11503,12 @@
       <c r="Q133" s="18" t="inlineStr"/>
       <c r="R133" s="18" t="inlineStr">
         <is>
-          <t>+919704444785</t>
+          <t>+919121300661</t>
         </is>
       </c>
       <c r="S133" s="17" t="inlineStr">
         <is>
-          <t>https://ramcorgroup.in/</t>
+          <t>https://vizagaerolabspvtltd.com/</t>
         </is>
       </c>
       <c r="T133" s="18" t="inlineStr"/>
@@ -11520,20 +11524,20 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>Vizag Aerolabs Private Limited</t>
+          <t>Vurimiai Global Services Private Limited</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>https://vizagaerolabspvtltd.com/</t>
+          <t>vurimiaiglobal.com</t>
         </is>
       </c>
       <c r="D134" s="11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>Visakhapatnam, India</t>
+          <t>Nellore, India</t>
         </is>
       </c>
       <c r="F134" s="14" t="inlineStr">
@@ -11558,17 +11562,17 @@
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drones; aerial surveying and mapping systems; drone repair components</t>
+          <t>Precision farming platforms; telemetry hardware; agricultural machinery</t>
         </is>
       </c>
       <c r="K134" s="14" t="inlineStr">
         <is>
-          <t>Drone repair, mapping, and technical support for agricultural and industrial operations</t>
+          <t>AI-powered precision agricultural deployment and localized tech integration</t>
         </is>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>DJI Agras drones, 2D and 3D mapping integrations, multispectral data support</t>
+          <t>Satellite imagery analytics integration, crop intelligence systems, agricultural drone platforms</t>
         </is>
       </c>
       <c r="M134" s="11" t="inlineStr">
@@ -11578,45 +11582,49 @@
       </c>
       <c r="N134" s="14" t="inlineStr"/>
       <c r="O134" s="14" t="inlineStr"/>
-      <c r="P134" s="14" t="inlineStr"/>
+      <c r="P134" s="13" t="inlineStr">
+        <is>
+          <t>nkantharao7@gmail.com</t>
+        </is>
+      </c>
       <c r="Q134" s="14" t="inlineStr"/>
-      <c r="R134" s="14" t="inlineStr">
-        <is>
-          <t>+919121300661</t>
-        </is>
-      </c>
+      <c r="R134" s="14" t="inlineStr"/>
       <c r="S134" s="13" t="inlineStr">
         <is>
-          <t>https://vizagaerolabspvtltd.com/</t>
-        </is>
-      </c>
-      <c r="T134" s="14" t="inlineStr"/>
+          <t>vurimiaiglobal.com</t>
+        </is>
+      </c>
+      <c r="T134" s="13" t="inlineStr">
+        <is>
+          <t>nkantharao7@gmail.com</t>
+        </is>
+      </c>
       <c r="U134" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="46.5" customHeight="1">
+    <row r="135" ht="33" customHeight="1">
       <c r="A135" s="15" t="n">
         <v>130</v>
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>Vurimiai Global Services Private Limited</t>
+          <t>DRONEEX</t>
         </is>
       </c>
       <c r="C135" s="17" t="inlineStr">
         <is>
-          <t>vurimiaiglobal.com</t>
+          <t>droneexshop.com</t>
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="E135" s="18" t="inlineStr">
         <is>
-          <t>Nellore, India</t>
+          <t>Thurimella, India</t>
         </is>
       </c>
       <c r="F135" s="18" t="inlineStr">
@@ -11641,69 +11649,73 @@
       </c>
       <c r="J135" s="18" t="inlineStr">
         <is>
-          <t>Precision farming platforms; telemetry hardware; agricultural machinery</t>
+          <t>Drone components; payloads; radio controllers; optics</t>
         </is>
       </c>
       <c r="K135" s="18" t="inlineStr">
         <is>
-          <t>AI-powered precision agricultural deployment and localized tech integration</t>
+          <t>Online distribution of high-end consumer and enterprise drone parts and payload sensors</t>
         </is>
       </c>
       <c r="L135" s="18" t="inlineStr">
         <is>
-          <t>Satellite imagery analytics integration, crop intelligence systems, agricultural drone platforms</t>
+          <t>DJI enterprise replacement parts, specialized carbon fiber props, telemetry antennas</t>
         </is>
       </c>
       <c r="M135" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N135" s="18" t="inlineStr"/>
-      <c r="O135" s="18" t="inlineStr"/>
-      <c r="P135" s="17" t="inlineStr">
-        <is>
-          <t>nkantharao7@gmail.com</t>
-        </is>
-      </c>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="N135" s="18" t="inlineStr">
+        <is>
+          <t>Vasu</t>
+        </is>
+      </c>
+      <c r="O135" s="18" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="P135" s="18" t="inlineStr"/>
       <c r="Q135" s="18" t="inlineStr"/>
-      <c r="R135" s="18" t="inlineStr"/>
+      <c r="R135" s="18" t="inlineStr">
+        <is>
+          <t>+91 81798 46276</t>
+        </is>
+      </c>
       <c r="S135" s="17" t="inlineStr">
         <is>
-          <t>vurimiaiglobal.com</t>
-        </is>
-      </c>
-      <c r="T135" s="17" t="inlineStr">
-        <is>
-          <t>nkantharao7@gmail.com</t>
-        </is>
-      </c>
+          <t>droneexshop.com</t>
+        </is>
+      </c>
+      <c r="T135" s="18" t="inlineStr"/>
       <c r="U135" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="33" customHeight="1">
+    <row r="136" ht="46.5" customHeight="1">
       <c r="A136" s="11" t="n">
         <v>131</v>
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>DRONEEX</t>
+          <t>Mana Rythu Drones</t>
         </is>
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>droneexshop.com</t>
+          <t>manarythudrones.com</t>
         </is>
       </c>
       <c r="D136" s="11" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>Thurimella, India</t>
+          <t>Guntur, India</t>
         </is>
       </c>
       <c r="F136" s="14" t="inlineStr">
@@ -11723,49 +11735,41 @@
       </c>
       <c r="I136" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>1-20</t>
         </is>
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>Drone components; payloads; radio controllers; optics</t>
+          <t>Crop spraying drones; quadcopters; drone spare parts</t>
         </is>
       </c>
       <c r="K136" s="14" t="inlineStr">
         <is>
-          <t>Online distribution of high-end consumer and enterprise drone parts and payload sensors</t>
+          <t>Providing commercial sales, field guidance, technical maintenance, and training for smart agriculture operations.</t>
         </is>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>DJI enterprise replacement parts, specialized carbon fiber props, telemetry antennas</t>
+          <t>Agricultural spraying drones; autonomous crop protection systems; drone batteries</t>
         </is>
       </c>
       <c r="M136" s="11" t="inlineStr">
         <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="N136" s="14" t="inlineStr">
-        <is>
-          <t>Vasu</t>
-        </is>
-      </c>
-      <c r="O136" s="14" t="inlineStr">
-        <is>
-          <t>Lead Engineer</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="N136" s="14" t="inlineStr"/>
+      <c r="O136" s="14" t="inlineStr"/>
       <c r="P136" s="14" t="inlineStr"/>
       <c r="Q136" s="14" t="inlineStr"/>
       <c r="R136" s="14" t="inlineStr">
         <is>
-          <t>+91 81798 46276</t>
+          <t>+91 97038 86677</t>
         </is>
       </c>
       <c r="S136" s="13" t="inlineStr">
         <is>
-          <t>droneexshop.com</t>
+          <t>manarythudrones.com</t>
         </is>
       </c>
       <c r="T136" s="14" t="inlineStr"/>
@@ -11775,18 +11779,18 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="46.5" customHeight="1">
+    <row r="137" ht="33" customHeight="1">
       <c r="A137" s="15" t="n">
         <v>132</v>
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>Mana Rythu Drones</t>
+          <t>Dji Drone Store (Nexor Drone)</t>
         </is>
       </c>
       <c r="C137" s="17" t="inlineStr">
         <is>
-          <t>manarythudrones.com</t>
+          <t>https://nexordrone.in</t>
         </is>
       </c>
       <c r="D137" s="15" t="n">
@@ -11794,7 +11798,7 @@
       </c>
       <c r="E137" s="18" t="inlineStr">
         <is>
-          <t>Guntur, India</t>
+          <t>Mohali, India</t>
         </is>
       </c>
       <c r="F137" s="18" t="inlineStr">
@@ -11814,22 +11818,22 @@
       </c>
       <c r="I137" s="15" t="inlineStr">
         <is>
-          <t>1-20</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J137" s="18" t="inlineStr">
         <is>
-          <t>Crop spraying drones; quadcopters; drone spare parts</t>
+          <t>Agricultural drones; aerial camera systems; drone accessories</t>
         </is>
       </c>
       <c r="K137" s="18" t="inlineStr">
         <is>
-          <t>Providing commercial sales, field guidance, technical maintenance, and training for smart agriculture operations.</t>
+          <t>Retail sales and distribution of commercial and consumer unmanned aerial systems.</t>
         </is>
       </c>
       <c r="L137" s="18" t="inlineStr">
         <is>
-          <t>Agricultural spraying drones; autonomous crop protection systems; drone batteries</t>
+          <t>DJI Agras T10, DJI Agras T30, DJI Agras T40, DJI Agras T50</t>
         </is>
       </c>
       <c r="M137" s="15" t="inlineStr">
@@ -11843,37 +11847,41 @@
       <c r="Q137" s="18" t="inlineStr"/>
       <c r="R137" s="18" t="inlineStr">
         <is>
-          <t>+91 97038 86677</t>
+          <t>+91 96437 44872</t>
         </is>
       </c>
       <c r="S137" s="17" t="inlineStr">
         <is>
-          <t>manarythudrones.com</t>
-        </is>
-      </c>
-      <c r="T137" s="18" t="inlineStr"/>
+          <t>https://nexordrone.in</t>
+        </is>
+      </c>
+      <c r="T137" s="17" t="inlineStr">
+        <is>
+          <t>djidronestore1@gmail.com</t>
+        </is>
+      </c>
       <c r="U137" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="33" customHeight="1">
+    <row r="138" ht="46.5" customHeight="1">
       <c r="A138" s="11" t="n">
         <v>133</v>
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>Dji Drone Store (Nexor Drone)</t>
+          <t>Drone Doctor</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>https://nexordrone.in</t>
+          <t>dronedoctorchd.com</t>
         </is>
       </c>
       <c r="D138" s="11" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
@@ -11902,17 +11910,17 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drones; aerial camera systems; drone accessories</t>
+          <t>Drone spare parts; intelligent flight batteries; gimbal assemblies</t>
         </is>
       </c>
       <c r="K138" s="14" t="inlineStr">
         <is>
-          <t>Retail sales and distribution of commercial and consumer unmanned aerial systems.</t>
+          <t>Sourcing and sales of original equipment manufacturer parts and specialized hardware diagnostics.</t>
         </is>
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>DJI Agras T10, DJI Agras T30, DJI Agras T40, DJI Agras T50</t>
+          <t>DJI replacement parts, intelligent flight batteries, landing gears, flight gimbals</t>
         </is>
       </c>
       <c r="M138" s="11" t="inlineStr">
@@ -11926,19 +11934,15 @@
       <c r="Q138" s="14" t="inlineStr"/>
       <c r="R138" s="14" t="inlineStr">
         <is>
-          <t>+91 96437 44872</t>
+          <t>+91 98150 69797</t>
         </is>
       </c>
       <c r="S138" s="13" t="inlineStr">
         <is>
-          <t>https://nexordrone.in</t>
-        </is>
-      </c>
-      <c r="T138" s="13" t="inlineStr">
-        <is>
-          <t>djidronestore1@gmail.com</t>
-        </is>
-      </c>
+          <t>dronedoctorchd.com</t>
+        </is>
+      </c>
+      <c r="T138" s="14" t="inlineStr"/>
       <c r="U138" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -11951,12 +11955,12 @@
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>Drone Doctor</t>
+          <t>AEROKART INDIA</t>
         </is>
       </c>
       <c r="C139" s="17" t="inlineStr">
         <is>
-          <t>dronedoctorchd.com</t>
+          <t>https://aerokartindia.in</t>
         </is>
       </c>
       <c r="D139" s="15" t="n">
@@ -11984,22 +11988,22 @@
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J139" s="18" t="inlineStr">
         <is>
-          <t>Drone spare parts; intelligent flight batteries; gimbal assemblies</t>
+          <t>Robotics hardware; brushless motors; electronic speed controllers (ESCs); drone kits</t>
         </is>
       </c>
       <c r="K139" s="18" t="inlineStr">
         <is>
-          <t>Sourcing and sales of original equipment manufacturer parts and specialized hardware diagnostics.</t>
+          <t>E-commerce distribution of components and multirotor electronics across regional markets.</t>
         </is>
       </c>
       <c r="L139" s="18" t="inlineStr">
         <is>
-          <t>DJI replacement parts, intelligent flight batteries, landing gears, flight gimbals</t>
+          <t>Aurelia X Pro systems, brushless DC motors, Simonk ESC controllers, multirotor propellers</t>
         </is>
       </c>
       <c r="M139" s="15" t="inlineStr">
@@ -12013,12 +12017,12 @@
       <c r="Q139" s="18" t="inlineStr"/>
       <c r="R139" s="18" t="inlineStr">
         <is>
-          <t>+91 98150 69797</t>
+          <t>+91 98147 27278</t>
         </is>
       </c>
       <c r="S139" s="17" t="inlineStr">
         <is>
-          <t>dronedoctorchd.com</t>
+          <t>https://aerokartindia.in</t>
         </is>
       </c>
       <c r="T139" s="18" t="inlineStr"/>
@@ -12034,20 +12038,20 @@
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t>AEROKART INDIA</t>
+          <t>RVS Led Display</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>https://aerokartindia.in</t>
+          <t>dronecameradelhi.com</t>
         </is>
       </c>
       <c r="D140" s="11" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>Mohali, India</t>
+          <t>Amritsar, India</t>
         </is>
       </c>
       <c r="F140" s="14" t="inlineStr">
@@ -12067,41 +12071,37 @@
       </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>Robotics hardware; brushless motors; electronic speed controllers (ESCs); drone kits</t>
+          <t>Commercial camera drones; content creation electronics; optical sensors</t>
         </is>
       </c>
       <c r="K140" s="14" t="inlineStr">
         <is>
-          <t>E-commerce distribution of components and multirotor electronics across regional markets.</t>
+          <t>Hardware trading, model onboarding, and retail sales of consumer-to-prosumer unmanned aircraft systems.</t>
         </is>
       </c>
       <c r="L140" s="14" t="inlineStr">
         <is>
-          <t>Aurelia X Pro systems, brushless DC motors, Simonk ESC controllers, multirotor propellers</t>
+          <t>DJI Air 3S, DJI Mini 4K, high-resolution imaging flight systems</t>
         </is>
       </c>
       <c r="M140" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N140" s="14" t="inlineStr"/>
       <c r="O140" s="14" t="inlineStr"/>
       <c r="P140" s="14" t="inlineStr"/>
       <c r="Q140" s="14" t="inlineStr"/>
-      <c r="R140" s="14" t="inlineStr">
-        <is>
-          <t>+91 98147 27278</t>
-        </is>
-      </c>
+      <c r="R140" s="14" t="inlineStr"/>
       <c r="S140" s="13" t="inlineStr">
         <is>
-          <t>https://aerokartindia.in</t>
+          <t>dronecameradelhi.com</t>
         </is>
       </c>
       <c r="T140" s="14" t="inlineStr"/>
@@ -12111,18 +12111,18 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="46.5" customHeight="1">
+    <row r="141" ht="33" customHeight="1">
       <c r="A141" s="15" t="n">
         <v>136</v>
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>RVS Led Display</t>
+          <t>Khurana Gadgets</t>
         </is>
       </c>
       <c r="C141" s="17" t="inlineStr">
         <is>
-          <t>dronecameradelhi.com</t>
+          <t>khuranagadgets.in</t>
         </is>
       </c>
       <c r="D141" s="15" t="n">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="E141" s="18" t="inlineStr">
         <is>
-          <t>Amritsar, India</t>
+          <t>Ludhiana, India</t>
         </is>
       </c>
       <c r="F141" s="18" t="inlineStr">
@@ -12155,32 +12155,36 @@
       </c>
       <c r="J141" s="18" t="inlineStr">
         <is>
-          <t>Commercial camera drones; content creation electronics; optical sensors</t>
+          <t>Consumer electronics; camera drones and spare parts</t>
         </is>
       </c>
       <c r="K141" s="18" t="inlineStr">
         <is>
-          <t>Hardware trading, model onboarding, and retail sales of consumer-to-prosumer unmanned aircraft systems.</t>
+          <t>Retail and wholesale supply of discounted smart gadgets and multi-rotor drones</t>
         </is>
       </c>
       <c r="L141" s="18" t="inlineStr">
         <is>
-          <t>DJI Air 3S, DJI Mini 4K, high-resolution imaging flight systems</t>
+          <t>DJI Mini 2, DJI Mavic, DJI Avata, E88 PRO MAX, and M3 MAX drones</t>
         </is>
       </c>
       <c r="M141" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N141" s="18" t="inlineStr"/>
       <c r="O141" s="18" t="inlineStr"/>
       <c r="P141" s="18" t="inlineStr"/>
       <c r="Q141" s="18" t="inlineStr"/>
-      <c r="R141" s="18" t="inlineStr"/>
+      <c r="R141" s="18" t="inlineStr">
+        <is>
+          <t>+916280867909</t>
+        </is>
+      </c>
       <c r="S141" s="17" t="inlineStr">
         <is>
-          <t>dronecameradelhi.com</t>
+          <t>khuranagadgets.in</t>
         </is>
       </c>
       <c r="T141" s="18" t="inlineStr"/>
@@ -12196,20 +12200,20 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t>Khurana Gadgets</t>
+          <t>Gurudrone Agritech Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>khuranagadgets.in</t>
+          <t>https://www.gurudrones.com</t>
         </is>
       </c>
       <c r="D142" s="11" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>Ludhiana, India</t>
+          <t>Kurukshetra, India</t>
         </is>
       </c>
       <c r="F142" s="14" t="inlineStr">
@@ -12229,22 +12233,22 @@
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>Consumer electronics; camera drones and spare parts</t>
+          <t>Agriculture drones; drone components and wholesale accessories</t>
         </is>
       </c>
       <c r="K142" s="14" t="inlineStr">
         <is>
-          <t>Retail and wholesale supply of discounted smart gadgets and multi-rotor drones</t>
+          <t>Supplying localized crop spraying technology and hardware maintenance kits</t>
         </is>
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
-          <t>DJI Mini 2, DJI Mavic, DJI Avata, E88 PRO MAX, and M3 MAX drones</t>
+          <t>Drone battery packs, remote controls, boom sprayer nozzles, IoTech World drone parts</t>
         </is>
       </c>
       <c r="M142" s="11" t="inlineStr">
@@ -12252,18 +12256,22 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N142" s="14" t="inlineStr"/>
-      <c r="O142" s="14" t="inlineStr"/>
+      <c r="N142" s="14" t="inlineStr">
+        <is>
+          <t>Jatinder Kumar</t>
+        </is>
+      </c>
+      <c r="O142" s="14" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
       <c r="P142" s="14" t="inlineStr"/>
       <c r="Q142" s="14" t="inlineStr"/>
-      <c r="R142" s="14" t="inlineStr">
-        <is>
-          <t>+916280867909</t>
-        </is>
-      </c>
+      <c r="R142" s="14" t="inlineStr"/>
       <c r="S142" s="13" t="inlineStr">
         <is>
-          <t>khuranagadgets.in</t>
+          <t>https://www.gurudrones.com</t>
         </is>
       </c>
       <c r="T142" s="14" t="inlineStr"/>
@@ -12273,26 +12281,26 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="33" customHeight="1">
+    <row r="143" ht="46.5" customHeight="1">
       <c r="A143" s="15" t="n">
         <v>138</v>
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>Gurudrone Agritech Pvt. Ltd.</t>
+          <t>Zion Technologies</t>
         </is>
       </c>
       <c r="C143" s="17" t="inlineStr">
         <is>
-          <t>https://www.gurudrones.com</t>
+          <t>ziontechnologies.in</t>
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>2024</v>
+        <v>1997</v>
       </c>
       <c r="E143" s="18" t="inlineStr">
         <is>
-          <t>Kurukshetra, India</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="F143" s="18" t="inlineStr">
@@ -12312,22 +12320,22 @@
       </c>
       <c r="I143" s="15" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J143" s="18" t="inlineStr">
         <is>
-          <t>Agriculture drones; drone components and wholesale accessories</t>
+          <t>Commercial drones; autonomous navigation systems; AR/VR spatial computing hardware</t>
         </is>
       </c>
       <c r="K143" s="18" t="inlineStr">
         <is>
-          <t>Supplying localized crop spraying technology and hardware maintenance kits</t>
+          <t>Supplying multi-industry enterprise drone technology and advanced hardware workflows</t>
         </is>
       </c>
       <c r="L143" s="18" t="inlineStr">
         <is>
-          <t>Drone battery packs, remote controls, boom sprayer nozzles, IoTech World drone parts</t>
+          <t>DJI Agras T16 spraying platforms, DroneAcharya agricultural mapping systems</t>
         </is>
       </c>
       <c r="M143" s="15" t="inlineStr">
@@ -12335,22 +12343,14 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N143" s="18" t="inlineStr">
-        <is>
-          <t>Jatinder Kumar</t>
-        </is>
-      </c>
-      <c r="O143" s="18" t="inlineStr">
-        <is>
-          <t>Founder &amp; CEO</t>
-        </is>
-      </c>
+      <c r="N143" s="18" t="inlineStr"/>
+      <c r="O143" s="18" t="inlineStr"/>
       <c r="P143" s="18" t="inlineStr"/>
       <c r="Q143" s="18" t="inlineStr"/>
       <c r="R143" s="18" t="inlineStr"/>
       <c r="S143" s="17" t="inlineStr">
         <is>
-          <t>https://www.gurudrones.com</t>
+          <t>ziontechnologies.in</t>
         </is>
       </c>
       <c r="T143" s="18" t="inlineStr"/>
@@ -12360,26 +12360,26 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="46.5" customHeight="1">
+    <row r="144" ht="33" customHeight="1">
       <c r="A144" s="11" t="n">
         <v>139</v>
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t>Zion Technologies</t>
+          <t>North East Drone Services</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>ziontechnologies.in</t>
+          <t>northeastdroneservices.in</t>
         </is>
       </c>
       <c r="D144" s="11" t="n">
-        <v>1997</v>
+        <v>2024</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Guwahati, India</t>
         </is>
       </c>
       <c r="F144" s="14" t="inlineStr">
@@ -12399,22 +12399,22 @@
       </c>
       <c r="I144" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>Commercial drones; autonomous navigation systems; AR/VR spatial computing hardware</t>
+          <t>Agricultural drones; aerial mapping hardware; drone accessories</t>
         </is>
       </c>
       <c r="K144" s="14" t="inlineStr">
         <is>
-          <t>Supplying multi-industry enterprise drone technology and advanced hardware workflows</t>
+          <t>UAV supply and technical support for crop monitoring and topographic mapping</t>
         </is>
       </c>
       <c r="L144" s="14" t="inlineStr">
         <is>
-          <t>DJI Agras T16 spraying platforms, DroneAcharya agricultural mapping systems</t>
+          <t>DJI drones, aerial mapping sensors, agricultural scouting systems</t>
         </is>
       </c>
       <c r="M144" s="11" t="inlineStr">
@@ -12422,14 +12422,26 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N144" s="14" t="inlineStr"/>
-      <c r="O144" s="14" t="inlineStr"/>
+      <c r="N144" s="14" t="inlineStr">
+        <is>
+          <t>Bhargav Bezbaruah</t>
+        </is>
+      </c>
+      <c r="O144" s="14" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="P144" s="14" t="inlineStr"/>
       <c r="Q144" s="14" t="inlineStr"/>
-      <c r="R144" s="14" t="inlineStr"/>
+      <c r="R144" s="14" t="inlineStr">
+        <is>
+          <t>+91 88226 23363</t>
+        </is>
+      </c>
       <c r="S144" s="13" t="inlineStr">
         <is>
-          <t>ziontechnologies.in</t>
+          <t>northeastdroneservices.in</t>
         </is>
       </c>
       <c r="T144" s="14" t="inlineStr"/>
@@ -12445,16 +12457,16 @@
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>North East Drone Services</t>
+          <t>G1Kart.com</t>
         </is>
       </c>
       <c r="C145" s="17" t="inlineStr">
         <is>
-          <t>northeastdroneservices.in</t>
+          <t>g1kart.com</t>
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E145" s="18" t="inlineStr">
         <is>
@@ -12478,22 +12490,22 @@
       </c>
       <c r="I145" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="J145" s="18" t="inlineStr">
         <is>
-          <t>Agricultural drones; aerial mapping hardware; drone accessories</t>
+          <t>UAV hardware; drone components; genuine parts</t>
         </is>
       </c>
       <c r="K145" s="18" t="inlineStr">
         <is>
-          <t>UAV supply and technical support for crop monitoring and topographic mapping</t>
+          <t>Commercial and consumer drone distribution, repair, and technical consultation</t>
         </is>
       </c>
       <c r="L145" s="18" t="inlineStr">
         <is>
-          <t>DJI drones, aerial mapping sensors, agricultural scouting systems</t>
+          <t>DJI Mini series, DJI enterprise platforms, drone replacement modules</t>
         </is>
       </c>
       <c r="M145" s="15" t="inlineStr">
@@ -12501,26 +12513,18 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N145" s="18" t="inlineStr">
-        <is>
-          <t>Bhargav Bezbaruah</t>
-        </is>
-      </c>
-      <c r="O145" s="18" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="N145" s="18" t="inlineStr"/>
+      <c r="O145" s="18" t="inlineStr"/>
       <c r="P145" s="18" t="inlineStr"/>
       <c r="Q145" s="18" t="inlineStr"/>
       <c r="R145" s="18" t="inlineStr">
         <is>
-          <t>+91 88226 23363</t>
+          <t>+91 98540 09009</t>
         </is>
       </c>
       <c r="S145" s="17" t="inlineStr">
         <is>
-          <t>northeastdroneservices.in</t>
+          <t>g1kart.com</t>
         </is>
       </c>
       <c r="T145" s="18" t="inlineStr"/>
@@ -12530,22 +12534,22 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="33" customHeight="1">
+    <row r="146" ht="46.5" customHeight="1">
       <c r="A146" s="11" t="n">
         <v>141</v>
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t>G1Kart.com</t>
+          <t>VRS Agritech Private Limited</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>g1kart.com</t>
+          <t>https://www.vrsagritech.com/</t>
         </is>
       </c>
       <c r="D146" s="11" t="n">
-        <v>2023</v>
+        <v>1984</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
@@ -12569,22 +12573,22 @@
       </c>
       <c r="I146" s="11" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>26-50</t>
         </is>
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>UAV hardware; drone components; genuine parts</t>
+          <t>Agricultural sprayers; Knapsack power sprayers; Battery operated sprayers; Agricultural machinery</t>
         </is>
       </c>
       <c r="K146" s="14" t="inlineStr">
         <is>
-          <t>Commercial and consumer drone distribution, repair, and technical consultation</t>
+          <t>Marketing and supply of agri-inputs, machinery, and farm technology solutions across Northeast India.</t>
         </is>
       </c>
       <c r="L146" s="14" t="inlineStr">
         <is>
-          <t>DJI Mini series, DJI enterprise platforms, drone replacement modules</t>
+          <t>Battery sprayers, mist blowers, manual and motorized knapsack crop sprayers.</t>
         </is>
       </c>
       <c r="M146" s="11" t="inlineStr">
@@ -12598,41 +12602,45 @@
       <c r="Q146" s="14" t="inlineStr"/>
       <c r="R146" s="14" t="inlineStr">
         <is>
-          <t>+91 98540 09009</t>
+          <t>+91 361 254 6611</t>
         </is>
       </c>
       <c r="S146" s="13" t="inlineStr">
         <is>
-          <t>g1kart.com</t>
-        </is>
-      </c>
-      <c r="T146" s="14" t="inlineStr"/>
+          <t>https://www.vrsagritech.com/</t>
+        </is>
+      </c>
+      <c r="T146" s="13" t="inlineStr">
+        <is>
+          <t>vrsagritech@vrsgroup.in</t>
+        </is>
+      </c>
       <c r="U146" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="46.5" customHeight="1">
+    <row r="147" ht="33" customHeight="1">
       <c r="A147" s="15" t="n">
         <v>142</v>
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>VRS Agritech Private Limited</t>
+          <t>DIRD India Private Limited</t>
         </is>
       </c>
       <c r="C147" s="17" t="inlineStr">
         <is>
-          <t>https://www.vrsagritech.com/</t>
+          <t>dird.co.in</t>
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>1984</v>
+        <v>2025</v>
       </c>
       <c r="E147" s="18" t="inlineStr">
         <is>
-          <t>Guwahati, India</t>
+          <t>Ranchi, India</t>
         </is>
       </c>
       <c r="F147" s="18" t="inlineStr">
@@ -12652,22 +12660,22 @@
       </c>
       <c r="I147" s="15" t="inlineStr">
         <is>
-          <t>26-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J147" s="18" t="inlineStr">
         <is>
-          <t>Agricultural sprayers; Knapsack power sprayers; Battery operated sprayers; Agricultural machinery</t>
+          <t>Agricultural drones; DIY training kits; drone spares and accessories</t>
         </is>
       </c>
       <c r="K147" s="18" t="inlineStr">
         <is>
-          <t>Marketing and supply of agri-inputs, machinery, and farm technology solutions across Northeast India.</t>
+          <t>Drone-as-a-Service and precision agricultural technology integration</t>
         </is>
       </c>
       <c r="L147" s="18" t="inlineStr">
         <is>
-          <t>Battery sprayers, mist blowers, manual and motorized knapsack crop sprayers.</t>
+          <t>Spraying, mapping, and surveillance drones, drone training kits, OEM-grade components</t>
         </is>
       </c>
       <c r="M147" s="15" t="inlineStr">
@@ -12679,21 +12687,13 @@
       <c r="O147" s="18" t="inlineStr"/>
       <c r="P147" s="18" t="inlineStr"/>
       <c r="Q147" s="18" t="inlineStr"/>
-      <c r="R147" s="18" t="inlineStr">
-        <is>
-          <t>+91 361 254 6611</t>
-        </is>
-      </c>
+      <c r="R147" s="18" t="inlineStr"/>
       <c r="S147" s="17" t="inlineStr">
         <is>
-          <t>https://www.vrsagritech.com/</t>
-        </is>
-      </c>
-      <c r="T147" s="17" t="inlineStr">
-        <is>
-          <t>vrsagritech@vrsgroup.in</t>
-        </is>
-      </c>
+          <t>dird.co.in</t>
+        </is>
+      </c>
+      <c r="T147" s="18" t="inlineStr"/>
       <c r="U147" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -12706,20 +12706,20 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t>DIRD India Private Limited</t>
+          <t>Goa Tractors Tillers &amp; Agencies</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>dird.co.in</t>
+          <t>https://goatractors.in</t>
         </is>
       </c>
       <c r="D148" s="11" t="n">
-        <v>2025</v>
+        <v>1987</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>Ranchi, India</t>
+          <t>Bardez, India</t>
         </is>
       </c>
       <c r="F148" s="14" t="inlineStr">
@@ -12739,22 +12739,22 @@
       </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>51-200</t>
         </is>
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drones; DIY training kits; drone spares and accessories</t>
+          <t>Agricultural machinery; crop protection sprayers; farm implements</t>
         </is>
       </c>
       <c r="K148" s="14" t="inlineStr">
         <is>
-          <t>Drone-as-a-Service and precision agricultural technology integration</t>
+          <t>Farming machinery and precision crop treatment equipment distribution</t>
         </is>
       </c>
       <c r="L148" s="14" t="inlineStr">
         <is>
-          <t>Spraying, mapping, and surveillance drones, drone training kits, OEM-grade components</t>
+          <t>Power sprayers, tillers, weeders, agricultural tools</t>
         </is>
       </c>
       <c r="M148" s="11" t="inlineStr">
@@ -12766,13 +12766,21 @@
       <c r="O148" s="14" t="inlineStr"/>
       <c r="P148" s="14" t="inlineStr"/>
       <c r="Q148" s="14" t="inlineStr"/>
-      <c r="R148" s="14" t="inlineStr"/>
+      <c r="R148" s="14" t="inlineStr">
+        <is>
+          <t>+91 832 225 7060</t>
+        </is>
+      </c>
       <c r="S148" s="13" t="inlineStr">
         <is>
-          <t>dird.co.in</t>
-        </is>
-      </c>
-      <c r="T148" s="14" t="inlineStr"/>
+          <t>https://goatractors.in</t>
+        </is>
+      </c>
+      <c r="T148" s="13" t="inlineStr">
+        <is>
+          <t>sales@goatractors.in</t>
+        </is>
+      </c>
       <c r="U148" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -12785,20 +12793,20 @@
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>Goa Tractors Tillers &amp; Agencies</t>
+          <t>Cam Clinic Pro Zone</t>
         </is>
       </c>
       <c r="C149" s="17" t="inlineStr">
         <is>
-          <t>https://goatractors.in</t>
+          <t>https://camclinic.in</t>
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>1987</v>
+        <v>2017</v>
       </c>
       <c r="E149" s="18" t="inlineStr">
         <is>
-          <t>Bardez, India</t>
+          <t>Panaji, India</t>
         </is>
       </c>
       <c r="F149" s="18" t="inlineStr">
@@ -12818,27 +12826,27 @@
       </c>
       <c r="I149" s="15" t="inlineStr">
         <is>
-          <t>51-200</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J149" s="18" t="inlineStr">
         <is>
-          <t>Agricultural machinery; crop protection sprayers; farm implements</t>
+          <t>Unmanned aerial hardware; specialized cameras; sensor assemblies</t>
         </is>
       </c>
       <c r="K149" s="18" t="inlineStr">
         <is>
-          <t>Farming machinery and precision crop treatment equipment distribution</t>
+          <t>Pro-tier imaging technology systems and localized client procurement support</t>
         </is>
       </c>
       <c r="L149" s="18" t="inlineStr">
         <is>
-          <t>Power sprayers, tillers, weeders, agricultural tools</t>
+          <t>DJI Mavic series drones, optical payloads, remote controller ecosystems</t>
         </is>
       </c>
       <c r="M149" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N149" s="18" t="inlineStr"/>
@@ -12847,163 +12855,155 @@
       <c r="Q149" s="18" t="inlineStr"/>
       <c r="R149" s="18" t="inlineStr">
         <is>
-          <t>+91 832 225 7060</t>
+          <t>+91 99231 33449</t>
         </is>
       </c>
       <c r="S149" s="17" t="inlineStr">
         <is>
-          <t>https://goatractors.in</t>
-        </is>
-      </c>
-      <c r="T149" s="17" t="inlineStr">
-        <is>
-          <t>sales@goatractors.in</t>
-        </is>
-      </c>
+          <t>https://camclinic.in</t>
+        </is>
+      </c>
+      <c r="T149" s="18" t="inlineStr"/>
       <c r="U149" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="33" customHeight="1">
+    <row r="150" ht="46.5" customHeight="1">
       <c r="A150" s="11" t="n">
         <v>145</v>
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t>Cam Clinic Pro Zone</t>
+          <t>Redington Limited</t>
         </is>
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>https://camclinic.in</t>
+          <t>https://redingtongroup.com</t>
         </is>
       </c>
       <c r="D150" s="11" t="n">
-        <v>2017</v>
+        <v>1993</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>Panaji, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F150" s="14" t="inlineStr">
         <is>
-          <t>APAC(India)</t>
+          <t>ME(United Arab Emirates, Saudi Arabia); APAC(India, Singapore)</t>
         </is>
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India; Singapore; United Arab Emirates; Saudi Arabia; Qatar; Oman; Kuwait</t>
         </is>
       </c>
       <c r="H150" s="14" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="I150" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1,000-5,000</t>
         </is>
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>Unmanned aerial hardware; specialized cameras; sensor assemblies</t>
+          <t>Enterprise tech distribution; automation solutions; industrial drone systems</t>
         </is>
       </c>
       <c r="K150" s="14" t="inlineStr">
         <is>
-          <t>Pro-tier imaging technology systems and localized client procurement support</t>
+          <t>Large-scale supply chain logistics and national technology deployment framework management</t>
         </is>
       </c>
       <c r="L150" s="14" t="inlineStr">
         <is>
-          <t>DJI Mavic series drones, optical payloads, remote controller ecosystems</t>
+          <t>Garuda Aerospace agricultural platforms, field intelligence frameworks</t>
         </is>
       </c>
       <c r="M150" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N150" s="14" t="inlineStr"/>
       <c r="O150" s="14" t="inlineStr"/>
       <c r="P150" s="14" t="inlineStr"/>
       <c r="Q150" s="14" t="inlineStr"/>
-      <c r="R150" s="14" t="inlineStr">
-        <is>
-          <t>+91 99231 33449</t>
-        </is>
-      </c>
+      <c r="R150" s="14" t="inlineStr"/>
       <c r="S150" s="13" t="inlineStr">
         <is>
-          <t>https://camclinic.in</t>
+          <t>https://redingtongroup.com</t>
         </is>
       </c>
       <c r="T150" s="14" t="inlineStr"/>
       <c r="U150" s="11" t="inlineStr">
         <is>
-          <t>+91 / IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="46.5" customHeight="1">
+          <t>+91 / IN; +65 / SG; +971 / AE; +966 / SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="33" customHeight="1">
       <c r="A151" s="15" t="n">
         <v>146</v>
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>Redington Limited</t>
+          <t>Darubrahma Automation Robotics Private Limited</t>
         </is>
       </c>
       <c r="C151" s="17" t="inlineStr">
         <is>
-          <t>https://redingtongroup.com</t>
+          <t>http://bookyourdrone.com</t>
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>1993</v>
+        <v>2019</v>
       </c>
       <c r="E151" s="18" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="F151" s="18" t="inlineStr">
         <is>
-          <t>ME(United Arab Emirates, Saudi Arabia); APAC(India, Singapore)</t>
+          <t>APAC(India)</t>
         </is>
       </c>
       <c r="G151" s="18" t="inlineStr">
         <is>
-          <t>India; Singapore; United Arab Emirates; Saudi Arabia; Qatar; Oman; Kuwait</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H151" s="18" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
-          <t>1,000-5,000</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J151" s="18" t="inlineStr">
         <is>
-          <t>Enterprise tech distribution; automation solutions; industrial drone systems</t>
+          <t>Agricultural surveillance drones; field mapping and survey hardware</t>
         </is>
       </c>
       <c r="K151" s="18" t="inlineStr">
         <is>
-          <t>Large-scale supply chain logistics and national technology deployment framework management</t>
+          <t>B2B trading and distribution of multi-rotor agricultural automation drone platforms</t>
         </is>
       </c>
       <c r="L151" s="18" t="inlineStr">
         <is>
-          <t>Garuda Aerospace agricultural platforms, field intelligence frameworks</t>
+          <t>EFT E610P, EFT E616P, EFT G420, EFT G630, EFT Z20</t>
         </is>
       </c>
       <c r="M151" s="15" t="inlineStr">
@@ -13011,43 +13011,51 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N151" s="18" t="inlineStr"/>
-      <c r="O151" s="18" t="inlineStr"/>
+      <c r="N151" s="18" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad Das</t>
+        </is>
+      </c>
+      <c r="O151" s="18" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
       <c r="P151" s="18" t="inlineStr"/>
       <c r="Q151" s="18" t="inlineStr"/>
       <c r="R151" s="18" t="inlineStr"/>
       <c r="S151" s="17" t="inlineStr">
         <is>
-          <t>https://redingtongroup.com</t>
+          <t>http://bookyourdrone.com</t>
         </is>
       </c>
       <c r="T151" s="18" t="inlineStr"/>
       <c r="U151" s="15" t="inlineStr">
         <is>
-          <t>+91 / IN; +65 / SG; +971 / AE; +966 / SA</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="33" customHeight="1">
+          <t>+91 / IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="46.5" customHeight="1">
       <c r="A152" s="11" t="n">
         <v>147</v>
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t>Darubrahma Automation Robotics Private Limited</t>
+          <t>Samson Agri Power Equipments Private Limited</t>
         </is>
       </c>
       <c r="C152" s="13" t="inlineStr">
         <is>
-          <t>http://bookyourdrone.com</t>
+          <t>https://samsonagri.in</t>
         </is>
       </c>
       <c r="D152" s="11" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>Bhubaneswar, India</t>
+          <t>Cuttack, India</t>
         </is>
       </c>
       <c r="F152" s="14" t="inlineStr">
@@ -13067,22 +13075,22 @@
       </c>
       <c r="I152" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>Agricultural surveillance drones; field mapping and survey hardware</t>
+          <t>Agricultural drones; tractors; combine harvesters; rice transplanters; rotavators</t>
         </is>
       </c>
       <c r="K152" s="14" t="inlineStr">
         <is>
-          <t>B2B trading and distribution of multi-rotor agricultural automation drone platforms</t>
+          <t>Crop cycle mechanisation and precision agricultural equipment distribution</t>
         </is>
       </c>
       <c r="L152" s="14" t="inlineStr">
         <is>
-          <t>EFT E610P, EFT E616P, EFT G420, EFT G630, EFT Z20</t>
+          <t>MARUT AG365H agricultural spraying drone, precision tray seeders, Kubota autonomous transplanters</t>
         </is>
       </c>
       <c r="M152" s="11" t="inlineStr">
@@ -13090,22 +13098,14 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N152" s="14" t="inlineStr">
-        <is>
-          <t>Rajendra Prasad Das</t>
-        </is>
-      </c>
-      <c r="O152" s="14" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+      <c r="N152" s="14" t="inlineStr"/>
+      <c r="O152" s="14" t="inlineStr"/>
       <c r="P152" s="14" t="inlineStr"/>
       <c r="Q152" s="14" t="inlineStr"/>
       <c r="R152" s="14" t="inlineStr"/>
       <c r="S152" s="13" t="inlineStr">
         <is>
-          <t>http://bookyourdrone.com</t>
+          <t>https://samsonagri.in</t>
         </is>
       </c>
       <c r="T152" s="14" t="inlineStr"/>
@@ -13121,20 +13121,20 @@
       </c>
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>Samson Agri Power Equipments Private Limited</t>
+          <t>Indian Hobby Center</t>
         </is>
       </c>
       <c r="C153" s="17" t="inlineStr">
         <is>
-          <t>https://samsonagri.in</t>
+          <t>indianhobbycenter.com</t>
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="E153" s="18" t="inlineStr">
         <is>
-          <t>Cuttack, India</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="F153" s="18" t="inlineStr">
@@ -13154,22 +13154,22 @@
       </c>
       <c r="I153" s="15" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J153" s="18" t="inlineStr">
         <is>
-          <t>Agricultural drones; tractors; combine harvesters; rice transplanters; rotavators</t>
+          <t>Robotic instrumentation kits; flight telemetry controllers; drone assembly parts and power distribution systems</t>
         </is>
       </c>
       <c r="K153" s="18" t="inlineStr">
         <is>
-          <t>Crop cycle mechanisation and precision agricultural equipment distribution</t>
+          <t>Reselling IoT hardware, DIY automation packages, and flight components for tech projects</t>
         </is>
       </c>
       <c r="L153" s="18" t="inlineStr">
         <is>
-          <t>MARUT AG365H agricultural spraying drone, precision tray seeders, Kubota autonomous transplanters</t>
+          <t>DJI RC-N2 remote controllers, specialized flight sensors, custom microcontrollers and multi-rotor electronic speed controllers</t>
         </is>
       </c>
       <c r="M153" s="15" t="inlineStr">
@@ -13179,41 +13179,53 @@
       </c>
       <c r="N153" s="18" t="inlineStr"/>
       <c r="O153" s="18" t="inlineStr"/>
-      <c r="P153" s="18" t="inlineStr"/>
+      <c r="P153" s="17" t="inlineStr">
+        <is>
+          <t>info@indianhobbycenter.com</t>
+        </is>
+      </c>
       <c r="Q153" s="18" t="inlineStr"/>
-      <c r="R153" s="18" t="inlineStr"/>
+      <c r="R153" s="18" t="inlineStr">
+        <is>
+          <t>+91 82499 31161</t>
+        </is>
+      </c>
       <c r="S153" s="17" t="inlineStr">
         <is>
-          <t>https://samsonagri.in</t>
-        </is>
-      </c>
-      <c r="T153" s="18" t="inlineStr"/>
+          <t>indianhobbycenter.com</t>
+        </is>
+      </c>
+      <c r="T153" s="17" t="inlineStr">
+        <is>
+          <t>info@indianhobbycenter.com</t>
+        </is>
+      </c>
       <c r="U153" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="46.5" customHeight="1">
+    <row r="154" ht="60" customHeight="1">
       <c r="A154" s="11" t="n">
         <v>149</v>
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t>Indian Hobby Center</t>
+          <t>The Orissa Implements</t>
         </is>
       </c>
       <c r="C154" s="13" t="inlineStr">
         <is>
-          <t>indianhobbycenter.com</t>
+          <t>khojakhoji.com</t>
         </is>
       </c>
       <c r="D154" s="11" t="n">
-        <v>2018</v>
+        <v>2007</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>Bhubaneswar, India</t>
+          <t>Cuttack, India</t>
         </is>
       </c>
       <c r="F154" s="14" t="inlineStr">
@@ -13233,78 +13245,70 @@
       </c>
       <c r="I154" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>5-20</t>
         </is>
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>Robotic instrumentation kits; flight telemetry controllers; drone assembly parts and power distribution systems</t>
+          <t>Crop protection implements; battery-operated orchard sprayers; fluid discharge systems and farm mechanization equipment</t>
         </is>
       </c>
       <c r="K154" s="14" t="inlineStr">
         <is>
-          <t>Reselling IoT hardware, DIY automation packages, and flight components for tech projects</t>
+          <t>Commercial supply of modern horticultural and precision agricultural machinery lines</t>
         </is>
       </c>
       <c r="L154" s="14" t="inlineStr">
         <is>
-          <t>DJI RC-N2 remote controllers, specialized flight sensors, custom microcontrollers and multi-rotor electronic speed controllers</t>
+          <t>Neptune high-pressure battery spray systems, mechanized fluid pumps and specialized crop dusting equipment</t>
         </is>
       </c>
       <c r="M154" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N154" s="14" t="inlineStr"/>
       <c r="O154" s="14" t="inlineStr"/>
-      <c r="P154" s="13" t="inlineStr">
-        <is>
-          <t>info@indianhobbycenter.com</t>
-        </is>
-      </c>
+      <c r="P154" s="14" t="inlineStr"/>
       <c r="Q154" s="14" t="inlineStr"/>
       <c r="R154" s="14" t="inlineStr">
         <is>
-          <t>+91 82499 31161</t>
+          <t>+91 671 242 1592</t>
         </is>
       </c>
       <c r="S154" s="13" t="inlineStr">
         <is>
-          <t>indianhobbycenter.com</t>
-        </is>
-      </c>
-      <c r="T154" s="13" t="inlineStr">
-        <is>
-          <t>info@indianhobbycenter.com</t>
-        </is>
-      </c>
+          <t>khojakhoji.com</t>
+        </is>
+      </c>
+      <c r="T154" s="14" t="inlineStr"/>
       <c r="U154" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
+    <row r="155" ht="33" customHeight="1">
       <c r="A155" s="15" t="n">
         <v>150</v>
       </c>
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>The Orissa Implements</t>
+          <t>Dji Drone Shop Bhubaneswar</t>
         </is>
       </c>
       <c r="C155" s="17" t="inlineStr">
         <is>
-          <t>khojakhoji.com</t>
+          <t>djidroneshop.in</t>
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>2007</v>
+        <v>2020</v>
       </c>
       <c r="E155" s="18" t="inlineStr">
         <is>
-          <t>Cuttack, India</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="F155" s="18" t="inlineStr">
@@ -13324,22 +13328,22 @@
       </c>
       <c r="I155" s="15" t="inlineStr">
         <is>
-          <t>5-20</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J155" s="18" t="inlineStr">
         <is>
-          <t>Crop protection implements; battery-operated orchard sprayers; fluid discharge systems and farm mechanization equipment</t>
+          <t>Aerial camera drones; Unmanned system components</t>
         </is>
       </c>
       <c r="K155" s="18" t="inlineStr">
         <is>
-          <t>Commercial supply of modern horticultural and precision agricultural machinery lines</t>
+          <t>Genuine product distribution and direct client drone consultations</t>
         </is>
       </c>
       <c r="L155" s="18" t="inlineStr">
         <is>
-          <t>Neptune high-pressure battery spray systems, mechanized fluid pumps and specialized crop dusting equipment</t>
+          <t>DJI Air 3, DJI Mavic series, aerial accessories</t>
         </is>
       </c>
       <c r="M155" s="15" t="inlineStr">
@@ -13353,12 +13357,12 @@
       <c r="Q155" s="18" t="inlineStr"/>
       <c r="R155" s="18" t="inlineStr">
         <is>
-          <t>+91 671 242 1592</t>
+          <t>+917008560260</t>
         </is>
       </c>
       <c r="S155" s="17" t="inlineStr">
         <is>
-          <t>khojakhoji.com</t>
+          <t>djidroneshop.in</t>
         </is>
       </c>
       <c r="T155" s="18" t="inlineStr"/>
@@ -13374,20 +13378,20 @@
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>Dji Drone Shop Bhubaneswar</t>
+          <t>Aryan Aviation</t>
         </is>
       </c>
       <c r="C156" s="13" t="inlineStr">
         <is>
-          <t>djidroneshop.in</t>
+          <t>aryanaviationindia.com</t>
         </is>
       </c>
       <c r="D156" s="11" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>Bhubaneswar, India</t>
+          <t>Raipur, India</t>
         </is>
       </c>
       <c r="F156" s="14" t="inlineStr">
@@ -13412,22 +13416,22 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>Aerial camera drones; Unmanned system components</t>
+          <t>Enterprise and consumer drones; drone components; aerial camera systems</t>
         </is>
       </c>
       <c r="K156" s="14" t="inlineStr">
         <is>
-          <t>Genuine product distribution and direct client drone consultations</t>
+          <t>Drone supply, accessories distribution, and hardware repair services</t>
         </is>
       </c>
       <c r="L156" s="14" t="inlineStr">
         <is>
-          <t>DJI Air 3, DJI Mavic series, aerial accessories</t>
+          <t>DJI Mavic series, DJI Phantom series, drone remote controllers, battery kits</t>
         </is>
       </c>
       <c r="M156" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N156" s="14" t="inlineStr"/>
@@ -13436,15 +13440,19 @@
       <c r="Q156" s="14" t="inlineStr"/>
       <c r="R156" s="14" t="inlineStr">
         <is>
-          <t>+917008560260</t>
+          <t>+917869332887</t>
         </is>
       </c>
       <c r="S156" s="13" t="inlineStr">
         <is>
-          <t>djidroneshop.in</t>
-        </is>
-      </c>
-      <c r="T156" s="14" t="inlineStr"/>
+          <t>aryanaviationindia.com</t>
+        </is>
+      </c>
+      <c r="T156" s="13" t="inlineStr">
+        <is>
+          <t>raipurpollutionshoot@gmail.com</t>
+        </is>
+      </c>
       <c r="U156" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -13457,20 +13465,20 @@
       </c>
       <c r="B157" s="16" t="inlineStr">
         <is>
-          <t>Aryan Aviation</t>
+          <t>Manish Marketing</t>
         </is>
       </c>
       <c r="C157" s="17" t="inlineStr">
         <is>
-          <t>aryanaviationindia.com</t>
+          <t>mmarketing.co.in</t>
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E157" s="18" t="inlineStr">
         <is>
-          <t>Raipur, India</t>
+          <t>Bilaspur, India</t>
         </is>
       </c>
       <c r="F157" s="18" t="inlineStr">
@@ -13495,17 +13503,17 @@
       </c>
       <c r="J157" s="18" t="inlineStr">
         <is>
-          <t>Enterprise and consumer drones; drone components; aerial camera systems</t>
+          <t>Agricultural sprayers; crop protection drones; petrol water pumps</t>
         </is>
       </c>
       <c r="K157" s="18" t="inlineStr">
         <is>
-          <t>Drone supply, accessories distribution, and hardware repair services</t>
+          <t>Wholesale distribution of agricultural crop spraying and watering technology</t>
         </is>
       </c>
       <c r="L157" s="18" t="inlineStr">
         <is>
-          <t>DJI Mavic series, DJI Phantom series, drone remote controllers, battery kits</t>
+          <t>10L Carbon Fiber Agriculture Spraying Drones, knapsack power sprayers</t>
         </is>
       </c>
       <c r="M157" s="15" t="inlineStr">
@@ -13513,25 +13521,29 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N157" s="18" t="inlineStr"/>
-      <c r="O157" s="18" t="inlineStr"/>
+      <c r="N157" s="18" t="inlineStr">
+        <is>
+          <t>Manish Singh</t>
+        </is>
+      </c>
+      <c r="O157" s="18" t="inlineStr">
+        <is>
+          <t>Proprietor</t>
+        </is>
+      </c>
       <c r="P157" s="18" t="inlineStr"/>
       <c r="Q157" s="18" t="inlineStr"/>
       <c r="R157" s="18" t="inlineStr">
         <is>
-          <t>+917869332887</t>
+          <t>+918071790105</t>
         </is>
       </c>
       <c r="S157" s="17" t="inlineStr">
         <is>
-          <t>aryanaviationindia.com</t>
-        </is>
-      </c>
-      <c r="T157" s="17" t="inlineStr">
-        <is>
-          <t>raipurpollutionshoot@gmail.com</t>
-        </is>
-      </c>
+          <t>mmarketing.co.in</t>
+        </is>
+      </c>
+      <c r="T157" s="18" t="inlineStr"/>
       <c r="U157" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -13544,20 +13556,20 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t>Manish Marketing</t>
+          <t>Akash Corporation</t>
         </is>
       </c>
       <c r="C158" s="13" t="inlineStr">
         <is>
-          <t>mmarketing.co.in</t>
+          <t>akashcorporation.com</t>
         </is>
       </c>
       <c r="D158" s="11" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>Bilaspur, India</t>
+          <t>Raipur, India</t>
         </is>
       </c>
       <c r="F158" s="14" t="inlineStr">
@@ -13582,17 +13594,17 @@
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>Agricultural sprayers; crop protection drones; petrol water pumps</t>
+          <t>Unmanned aerial hardware; industrial electronics; crop care systems</t>
         </is>
       </c>
       <c r="K158" s="14" t="inlineStr">
         <is>
-          <t>Wholesale distribution of agricultural crop spraying and watering technology</t>
+          <t>Supply of commercial and precision agricultural drone systems</t>
         </is>
       </c>
       <c r="L158" s="14" t="inlineStr">
         <is>
-          <t>10L Carbon Fiber Agriculture Spraying Drones, knapsack power sprayers</t>
+          <t>Multi-rotor agricultural spray drones, autonomous flight controllers</t>
         </is>
       </c>
       <c r="M158" s="11" t="inlineStr">
@@ -13600,26 +13612,18 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N158" s="14" t="inlineStr">
-        <is>
-          <t>Manish Singh</t>
-        </is>
-      </c>
-      <c r="O158" s="14" t="inlineStr">
-        <is>
-          <t>Proprietor</t>
-        </is>
-      </c>
+      <c r="N158" s="14" t="inlineStr"/>
+      <c r="O158" s="14" t="inlineStr"/>
       <c r="P158" s="14" t="inlineStr"/>
       <c r="Q158" s="14" t="inlineStr"/>
       <c r="R158" s="14" t="inlineStr">
         <is>
-          <t>+918071790105</t>
+          <t>+918103090932</t>
         </is>
       </c>
       <c r="S158" s="13" t="inlineStr">
         <is>
-          <t>mmarketing.co.in</t>
+          <t>akashcorporation.com</t>
         </is>
       </c>
       <c r="T158" s="14" t="inlineStr"/>
@@ -13635,16 +13639,16 @@
       </c>
       <c r="B159" s="16" t="inlineStr">
         <is>
-          <t>Akash Corporation</t>
+          <t>Madhu Agri Seeds</t>
         </is>
       </c>
       <c r="C159" s="17" t="inlineStr">
         <is>
-          <t>akashcorporation.com</t>
+          <t>avnsuppliers.com</t>
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E159" s="18" t="inlineStr">
         <is>
@@ -13673,17 +13677,17 @@
       </c>
       <c r="J159" s="18" t="inlineStr">
         <is>
-          <t>Unmanned aerial hardware; industrial electronics; crop care systems</t>
+          <t>Agricultural drones; crop protection spraying systems</t>
         </is>
       </c>
       <c r="K159" s="18" t="inlineStr">
         <is>
-          <t>Supply of commercial and precision agricultural drone systems</t>
+          <t>Precision agriculture drone distribution and high-quality seed supply</t>
         </is>
       </c>
       <c r="L159" s="18" t="inlineStr">
         <is>
-          <t>Multi-rotor agricultural spray drones, autonomous flight controllers</t>
+          <t>Marut Drones AG365S; drone-based autonomous crop spraying platforms</t>
         </is>
       </c>
       <c r="M159" s="15" t="inlineStr">
@@ -13691,18 +13695,22 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N159" s="18" t="inlineStr"/>
+      <c r="N159" s="18" t="inlineStr">
+        <is>
+          <t>AMIT KUMAR YADU</t>
+        </is>
+      </c>
       <c r="O159" s="18" t="inlineStr"/>
       <c r="P159" s="18" t="inlineStr"/>
       <c r="Q159" s="18" t="inlineStr"/>
       <c r="R159" s="18" t="inlineStr">
         <is>
-          <t>+918103090932</t>
+          <t>+91 97527 88288</t>
         </is>
       </c>
       <c r="S159" s="17" t="inlineStr">
         <is>
-          <t>akashcorporation.com</t>
+          <t>avnsuppliers.com</t>
         </is>
       </c>
       <c r="T159" s="18" t="inlineStr"/>
@@ -13718,16 +13726,16 @@
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t>Madhu Agri Seeds</t>
+          <t>Sai Baba Electronics</t>
         </is>
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>avnsuppliers.com</t>
+          <t>saibabaelectronics.in</t>
         </is>
       </c>
       <c r="D160" s="11" t="n">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
@@ -13756,17 +13764,17 @@
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drones; crop protection spraying systems</t>
+          <t>Unmanned aerial vehicles; drone components; imaging sensors</t>
         </is>
       </c>
       <c r="K160" s="14" t="inlineStr">
         <is>
-          <t>Precision agriculture drone distribution and high-quality seed supply</t>
+          <t>Drone sales, technical support, and precision electronics repair</t>
         </is>
       </c>
       <c r="L160" s="14" t="inlineStr">
         <is>
-          <t>Marut Drones AG365S; drone-based autonomous crop spraying platforms</t>
+          <t>DJI Air and Mavic series quadcopters; specialized drone payloads and controllers</t>
         </is>
       </c>
       <c r="M160" s="11" t="inlineStr">
@@ -13774,22 +13782,18 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N160" s="14" t="inlineStr">
-        <is>
-          <t>AMIT KUMAR YADU</t>
-        </is>
-      </c>
+      <c r="N160" s="14" t="inlineStr"/>
       <c r="O160" s="14" t="inlineStr"/>
       <c r="P160" s="14" t="inlineStr"/>
       <c r="Q160" s="14" t="inlineStr"/>
       <c r="R160" s="14" t="inlineStr">
         <is>
-          <t>+91 97527 88288</t>
+          <t>+91 98933 32458</t>
         </is>
       </c>
       <c r="S160" s="13" t="inlineStr">
         <is>
-          <t>avnsuppliers.com</t>
+          <t>saibabaelectronics.in</t>
         </is>
       </c>
       <c r="T160" s="14" t="inlineStr"/>
@@ -13805,16 +13809,16 @@
       </c>
       <c r="B161" s="16" t="inlineStr">
         <is>
-          <t>Sai Baba Electronics</t>
+          <t>Reliable Distributor</t>
         </is>
       </c>
       <c r="C161" s="17" t="inlineStr">
         <is>
-          <t>saibabaelectronics.in</t>
+          <t>reliableagrogroup.com</t>
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="E161" s="18" t="inlineStr">
         <is>
@@ -13838,41 +13842,49 @@
       </c>
       <c r="I161" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J161" s="18" t="inlineStr">
         <is>
-          <t>Unmanned aerial vehicles; drone components; imaging sensors</t>
+          <t>Agricultural machinery; power sprayers; farm mechanization tools</t>
         </is>
       </c>
       <c r="K161" s="18" t="inlineStr">
         <is>
-          <t>Drone sales, technical support, and precision electronics repair</t>
+          <t>Advanced agricultural machinery distribution and crop management equipment</t>
         </is>
       </c>
       <c r="L161" s="18" t="inlineStr">
         <is>
-          <t>DJI Air and Mavic series quadcopters; specialized drone payloads and controllers</t>
+          <t>Lovol combine harvesters; Kamco power tillers and mechanical sprayers</t>
         </is>
       </c>
       <c r="M161" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N161" s="18" t="inlineStr"/>
-      <c r="O161" s="18" t="inlineStr"/>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N161" s="18" t="inlineStr">
+        <is>
+          <t>Pawan Kumar Poddar</t>
+        </is>
+      </c>
+      <c r="O161" s="18" t="inlineStr">
+        <is>
+          <t>Proprietor</t>
+        </is>
+      </c>
       <c r="P161" s="18" t="inlineStr"/>
       <c r="Q161" s="18" t="inlineStr"/>
       <c r="R161" s="18" t="inlineStr">
         <is>
-          <t>+91 98933 32458</t>
+          <t>+91 78801 49170</t>
         </is>
       </c>
       <c r="S161" s="17" t="inlineStr">
         <is>
-          <t>saibabaelectronics.in</t>
+          <t>reliableagrogroup.com</t>
         </is>
       </c>
       <c r="T161" s="18" t="inlineStr"/>
@@ -13882,22 +13894,22 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="33" customHeight="1">
+    <row r="162" ht="46.5" customHeight="1">
       <c r="A162" s="11" t="n">
         <v>157</v>
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t>Reliable Distributor</t>
+          <t>Cropspoint Advance Solution Pvt Ltd</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>reliableagrogroup.com</t>
+          <t>krishisuvidha.com</t>
         </is>
       </c>
       <c r="D162" s="11" t="n">
-        <v>2003</v>
+        <v>2020</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
@@ -13921,49 +13933,41 @@
       </c>
       <c r="I162" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>Agricultural machinery; power sprayers; farm mechanization tools</t>
+          <t>Agricultural crop-spraying drones; crop health monitoring software; drone spare parts</t>
         </is>
       </c>
       <c r="K162" s="14" t="inlineStr">
         <is>
-          <t>Advanced agricultural machinery distribution and crop management equipment</t>
+          <t>Phygital distribution network and precision agriculture drone deployment for regional farmers.</t>
         </is>
       </c>
       <c r="L162" s="14" t="inlineStr">
         <is>
-          <t>Lovol combine harvesters; Kamco power tillers and mechanical sprayers</t>
+          <t>Crop spraying systems, multispectral crop analytics platforms, autonomous flight telemetry integration.</t>
         </is>
       </c>
       <c r="M162" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="N162" s="14" t="inlineStr">
-        <is>
-          <t>Pawan Kumar Poddar</t>
-        </is>
-      </c>
-      <c r="O162" s="14" t="inlineStr">
-        <is>
-          <t>Proprietor</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="N162" s="14" t="inlineStr"/>
+      <c r="O162" s="14" t="inlineStr"/>
       <c r="P162" s="14" t="inlineStr"/>
       <c r="Q162" s="14" t="inlineStr"/>
       <c r="R162" s="14" t="inlineStr">
         <is>
-          <t>+91 78801 49170</t>
+          <t>+91 82072 25432</t>
         </is>
       </c>
       <c r="S162" s="13" t="inlineStr">
         <is>
-          <t>reliableagrogroup.com</t>
+          <t>krishisuvidha.com</t>
         </is>
       </c>
       <c r="T162" s="14" t="inlineStr"/>
@@ -13973,18 +13977,18 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="46.5" customHeight="1">
+    <row r="163" ht="33" customHeight="1">
       <c r="A163" s="15" t="n">
         <v>158</v>
       </c>
       <c r="B163" s="16" t="inlineStr">
         <is>
-          <t>Cropspoint Advance Solution Pvt Ltd</t>
+          <t>BUY-LA</t>
         </is>
       </c>
       <c r="C163" s="17" t="inlineStr">
         <is>
-          <t>krishisuvidha.com</t>
+          <t>buy-la.in</t>
         </is>
       </c>
       <c r="D163" s="15" t="n">
@@ -14012,22 +14016,22 @@
       </c>
       <c r="I163" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J163" s="18" t="inlineStr">
         <is>
-          <t>Agricultural crop-spraying drones; crop health monitoring software; drone spare parts</t>
+          <t>Computer hardware; networking systems; robotics and drone cameras</t>
         </is>
       </c>
       <c r="K163" s="18" t="inlineStr">
         <is>
-          <t>Phygital distribution network and precision agriculture drone deployment for regional farmers.</t>
+          <t>Commercial IT infrastructure setup and advanced consumer robotics retail</t>
         </is>
       </c>
       <c r="L163" s="18" t="inlineStr">
         <is>
-          <t>Crop spraying systems, multispectral crop analytics platforms, autonomous flight telemetry integration.</t>
+          <t>Drone cameras, corporate networking hardware, productivity software systems</t>
         </is>
       </c>
       <c r="M163" s="15" t="inlineStr">
@@ -14039,14 +14043,10 @@
       <c r="O163" s="18" t="inlineStr"/>
       <c r="P163" s="18" t="inlineStr"/>
       <c r="Q163" s="18" t="inlineStr"/>
-      <c r="R163" s="18" t="inlineStr">
-        <is>
-          <t>+91 82072 25432</t>
-        </is>
-      </c>
+      <c r="R163" s="18" t="inlineStr"/>
       <c r="S163" s="17" t="inlineStr">
         <is>
-          <t>krishisuvidha.com</t>
+          <t>buy-la.in</t>
         </is>
       </c>
       <c r="T163" s="18" t="inlineStr"/>
@@ -14062,12 +14062,12 @@
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t>BUY-LA</t>
+          <t>Mega Drones</t>
         </is>
       </c>
       <c r="C164" s="13" t="inlineStr">
         <is>
-          <t>buy-la.in</t>
+          <t>megadrone.in</t>
         </is>
       </c>
       <c r="D164" s="11" t="n">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>Raipur, India</t>
+          <t>Dehradun, India</t>
         </is>
       </c>
       <c r="F164" s="14" t="inlineStr">
@@ -14095,22 +14095,22 @@
       </c>
       <c r="I164" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>Computer hardware; networking systems; robotics and drone cameras</t>
+          <t>Multirotor drones; stabilization gimbals</t>
         </is>
       </c>
       <c r="K164" s="14" t="inlineStr">
         <is>
-          <t>Commercial IT infrastructure setup and advanced consumer robotics retail</t>
+          <t>Distribution of commercial unmanned flight hardware and systems integration</t>
         </is>
       </c>
       <c r="L164" s="14" t="inlineStr">
         <is>
-          <t>Drone cameras, corporate networking hardware, productivity software systems</t>
+          <t>DJI systems, UDI RC aircraft</t>
         </is>
       </c>
       <c r="M164" s="11" t="inlineStr">
@@ -14122,10 +14122,14 @@
       <c r="O164" s="14" t="inlineStr"/>
       <c r="P164" s="14" t="inlineStr"/>
       <c r="Q164" s="14" t="inlineStr"/>
-      <c r="R164" s="14" t="inlineStr"/>
+      <c r="R164" s="14" t="inlineStr">
+        <is>
+          <t>+918077785974</t>
+        </is>
+      </c>
       <c r="S164" s="13" t="inlineStr">
         <is>
-          <t>buy-la.in</t>
+          <t>megadrone.in</t>
         </is>
       </c>
       <c r="T164" s="14" t="inlineStr"/>
@@ -14135,26 +14139,26 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="33" customHeight="1">
+    <row r="165" ht="46.5" customHeight="1">
       <c r="A165" s="15" t="n">
         <v>160</v>
       </c>
       <c r="B165" s="16" t="inlineStr">
         <is>
-          <t>Mega Drones</t>
+          <t>Aerodrone India</t>
         </is>
       </c>
       <c r="C165" s="17" t="inlineStr">
         <is>
-          <t>megadrone.in</t>
+          <t>aerodrone.in</t>
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E165" s="18" t="inlineStr">
         <is>
-          <t>Dehradun, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F165" s="18" t="inlineStr">
@@ -14174,22 +14178,22 @@
       </c>
       <c r="I165" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>5-20</t>
         </is>
       </c>
       <c r="J165" s="18" t="inlineStr">
         <is>
-          <t>Multirotor drones; stabilization gimbals</t>
+          <t>Foldable agricultural drone frames; chemical-resistant spray tanks; high-flow liquid flow sensors</t>
         </is>
       </c>
       <c r="K165" s="18" t="inlineStr">
         <is>
-          <t>Distribution of commercial unmanned flight hardware and systems integration</t>
+          <t>UAV custom component retail, high-thrust spray hardware distribution, and carbon-fiber agriculture assembly distribution</t>
         </is>
       </c>
       <c r="L165" s="18" t="inlineStr">
         <is>
-          <t>DJI systems, UDI RC aircraft</t>
+          <t>EFT G18 20L Frame, EFT E616P 16L Frame, Hobbywing 9L Centrifugal Nozzles, M30 Heavy Payload Kits</t>
         </is>
       </c>
       <c r="M165" s="15" t="inlineStr">
@@ -14201,14 +14205,10 @@
       <c r="O165" s="18" t="inlineStr"/>
       <c r="P165" s="18" t="inlineStr"/>
       <c r="Q165" s="18" t="inlineStr"/>
-      <c r="R165" s="18" t="inlineStr">
-        <is>
-          <t>+918077785974</t>
-        </is>
-      </c>
+      <c r="R165" s="18" t="inlineStr"/>
       <c r="S165" s="17" t="inlineStr">
         <is>
-          <t>megadrone.in</t>
+          <t>aerodrone.in</t>
         </is>
       </c>
       <c r="T165" s="18" t="inlineStr"/>
@@ -14224,20 +14224,20 @@
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t>Aerodrone India</t>
+          <t>Skytek Drones and Cinematography</t>
         </is>
       </c>
       <c r="C166" s="13" t="inlineStr">
         <is>
-          <t>aerodrone.in</t>
+          <t>360reels.com</t>
         </is>
       </c>
       <c r="D166" s="11" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Margao, India</t>
         </is>
       </c>
       <c r="F166" s="14" t="inlineStr">
@@ -14257,22 +14257,22 @@
       </c>
       <c r="I166" s="11" t="inlineStr">
         <is>
-          <t>5-20</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>Foldable agricultural drone frames; chemical-resistant spray tanks; high-flow liquid flow sensors</t>
+          <t>Enterprise mapping drones; multi-rotor imaging platforms; aerial surveillance equipment</t>
         </is>
       </c>
       <c r="K166" s="14" t="inlineStr">
         <is>
-          <t>UAV custom component retail, high-thrust spray hardware distribution, and carbon-fiber agriculture assembly distribution</t>
+          <t>Photogrammetry, spatial analytics hardware sourcing, and aerial integration services</t>
         </is>
       </c>
       <c r="L166" s="14" t="inlineStr">
         <is>
-          <t>EFT G18 20L Frame, EFT E616P 16L Frame, Hobbywing 9L Centrifugal Nozzles, M30 Heavy Payload Kits</t>
+          <t>DJI Matrice 300 RTK, DJI Mavic 3 Enterprise, and localized terrain photogrammetry packages</t>
         </is>
       </c>
       <c r="M166" s="11" t="inlineStr">
@@ -14284,10 +14284,14 @@
       <c r="O166" s="14" t="inlineStr"/>
       <c r="P166" s="14" t="inlineStr"/>
       <c r="Q166" s="14" t="inlineStr"/>
-      <c r="R166" s="14" t="inlineStr"/>
+      <c r="R166" s="14" t="inlineStr">
+        <is>
+          <t>+91 70200 63445</t>
+        </is>
+      </c>
       <c r="S166" s="13" t="inlineStr">
         <is>
-          <t>aerodrone.in</t>
+          <t>360reels.com</t>
         </is>
       </c>
       <c r="T166" s="14" t="inlineStr"/>
@@ -14303,20 +14307,20 @@
       </c>
       <c r="B167" s="16" t="inlineStr">
         <is>
-          <t>Skytek Drones and Cinematography</t>
+          <t>Tiwari Traders</t>
         </is>
       </c>
       <c r="C167" s="17" t="inlineStr">
         <is>
-          <t>360reels.com</t>
+          <t>tiwaritraders.in</t>
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="E167" s="18" t="inlineStr">
         <is>
-          <t>Margao, India</t>
+          <t>Patna, India</t>
         </is>
       </c>
       <c r="F167" s="18" t="inlineStr">
@@ -14336,22 +14340,22 @@
       </c>
       <c r="I167" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J167" s="18" t="inlineStr">
         <is>
-          <t>Enterprise mapping drones; multi-rotor imaging platforms; aerial surveillance equipment</t>
+          <t>Commercial drones; multi-spectral imaging payloads; crop monitoring sensors</t>
         </is>
       </c>
       <c r="K167" s="18" t="inlineStr">
         <is>
-          <t>Photogrammetry, spatial analytics hardware sourcing, and aerial integration services</t>
+          <t>Authorized sales, hands-on demonstration, and local distribution of consumer and commercial aerial hardware.</t>
         </is>
       </c>
       <c r="L167" s="18" t="inlineStr">
         <is>
-          <t>DJI Matrice 300 RTK, DJI Mavic 3 Enterprise, and localized terrain photogrammetry packages</t>
+          <t>DJI Agras T50, DJI Agras T30, DJI Mavic 3 Multispectral for precision agriculture applications</t>
         </is>
       </c>
       <c r="M167" s="15" t="inlineStr">
@@ -14361,19 +14365,27 @@
       </c>
       <c r="N167" s="18" t="inlineStr"/>
       <c r="O167" s="18" t="inlineStr"/>
-      <c r="P167" s="18" t="inlineStr"/>
+      <c r="P167" s="17" t="inlineStr">
+        <is>
+          <t>tiwariinfo@gmail.com</t>
+        </is>
+      </c>
       <c r="Q167" s="18" t="inlineStr"/>
       <c r="R167" s="18" t="inlineStr">
         <is>
-          <t>+91 70200 63445</t>
+          <t>+917909048524</t>
         </is>
       </c>
       <c r="S167" s="17" t="inlineStr">
         <is>
-          <t>360reels.com</t>
-        </is>
-      </c>
-      <c r="T167" s="18" t="inlineStr"/>
+          <t>tiwaritraders.in</t>
+        </is>
+      </c>
+      <c r="T167" s="17" t="inlineStr">
+        <is>
+          <t>tiwariinfo@gmail.com</t>
+        </is>
+      </c>
       <c r="U167" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14386,20 +14398,20 @@
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t>Tiwari Traders</t>
+          <t>Robokits India</t>
         </is>
       </c>
       <c r="C168" s="13" t="inlineStr">
         <is>
-          <t>tiwaritraders.in</t>
+          <t>robokits.co.in</t>
         </is>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2020</v>
+        <v>2007</v>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>Patna, India</t>
+          <t>Gandhinagar, India</t>
         </is>
       </c>
       <c r="F168" s="14" t="inlineStr">
@@ -14419,22 +14431,22 @@
       </c>
       <c r="I168" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>Commercial drones; multi-spectral imaging payloads; crop monitoring sensors</t>
+          <t>Agriculture drone carbon-fiber frames; drone electronic speed controllers</t>
         </is>
       </c>
       <c r="K168" s="14" t="inlineStr">
         <is>
-          <t>Authorized sales, hands-on demonstration, and local distribution of consumer and commercial aerial hardware.</t>
+          <t>B2B robotics component distribution supplying raw platform architecture for drone automation applications.</t>
         </is>
       </c>
       <c r="L168" s="14" t="inlineStr">
         <is>
-          <t>DJI Agras T50, DJI Agras T30, DJI Mavic 3 Multispectral for precision agriculture applications</t>
+          <t>EFT E Series E610P 10L Frame</t>
         </is>
       </c>
       <c r="M168" s="11" t="inlineStr">
@@ -14444,53 +14456,41 @@
       </c>
       <c r="N168" s="14" t="inlineStr"/>
       <c r="O168" s="14" t="inlineStr"/>
-      <c r="P168" s="13" t="inlineStr">
-        <is>
-          <t>tiwariinfo@gmail.com</t>
-        </is>
-      </c>
+      <c r="P168" s="14" t="inlineStr"/>
       <c r="Q168" s="14" t="inlineStr"/>
-      <c r="R168" s="14" t="inlineStr">
-        <is>
-          <t>+917909048524</t>
-        </is>
-      </c>
+      <c r="R168" s="14" t="inlineStr"/>
       <c r="S168" s="13" t="inlineStr">
         <is>
-          <t>tiwaritraders.in</t>
-        </is>
-      </c>
-      <c r="T168" s="13" t="inlineStr">
-        <is>
-          <t>tiwariinfo@gmail.com</t>
-        </is>
-      </c>
+          <t>robokits.co.in</t>
+        </is>
+      </c>
+      <c r="T168" s="14" t="inlineStr"/>
       <c r="U168" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="46.5" customHeight="1">
+    <row r="169" ht="33" customHeight="1">
       <c r="A169" s="15" t="n">
         <v>164</v>
       </c>
       <c r="B169" s="16" t="inlineStr">
         <is>
-          <t>Robokits India</t>
+          <t>All About Fly</t>
         </is>
       </c>
       <c r="C169" s="17" t="inlineStr">
         <is>
-          <t>robokits.co.in</t>
+          <t>allaboutfly.co.in</t>
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="E169" s="18" t="inlineStr">
         <is>
-          <t>Gandhinagar, India</t>
+          <t>Ghaziabad, India</t>
         </is>
       </c>
       <c r="F169" s="18" t="inlineStr">
@@ -14510,22 +14510,22 @@
       </c>
       <c r="I169" s="15" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J169" s="18" t="inlineStr">
         <is>
-          <t>Agriculture drone carbon-fiber frames; drone electronic speed controllers</t>
+          <t>Agricultural drone sprayers; drone components; lithium polymer batteries</t>
         </is>
       </c>
       <c r="K169" s="18" t="inlineStr">
         <is>
-          <t>B2B robotics component distribution supplying raw platform architecture for drone automation applications.</t>
+          <t>Commercial supply of unmanned aerial vehicle accessories and power systems</t>
         </is>
       </c>
       <c r="L169" s="18" t="inlineStr">
         <is>
-          <t>EFT E Series E610P 10L Frame</t>
+          <t>Agricultural drone sprayers, DJI battery kits, Mavic 3 Enterprise battery kits</t>
         </is>
       </c>
       <c r="M169" s="15" t="inlineStr">
@@ -14533,14 +14533,26 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N169" s="18" t="inlineStr"/>
-      <c r="O169" s="18" t="inlineStr"/>
+      <c r="N169" s="18" t="inlineStr">
+        <is>
+          <t>Mr. Nonu</t>
+        </is>
+      </c>
+      <c r="O169" s="18" t="inlineStr">
+        <is>
+          <t>Proprietor</t>
+        </is>
+      </c>
       <c r="P169" s="18" t="inlineStr"/>
       <c r="Q169" s="18" t="inlineStr"/>
-      <c r="R169" s="18" t="inlineStr"/>
+      <c r="R169" s="18" t="inlineStr">
+        <is>
+          <t>08045804524</t>
+        </is>
+      </c>
       <c r="S169" s="17" t="inlineStr">
         <is>
-          <t>robokits.co.in</t>
+          <t>allaboutfly.co.in</t>
         </is>
       </c>
       <c r="T169" s="18" t="inlineStr"/>
@@ -14550,26 +14562,26 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="33" customHeight="1">
+    <row r="170" ht="46.5" customHeight="1">
       <c r="A170" s="11" t="n">
         <v>165</v>
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t>All About Fly</t>
+          <t>V Drone Tech</t>
         </is>
       </c>
       <c r="C170" s="13" t="inlineStr">
         <is>
-          <t>allaboutfly.co.in</t>
+          <t>vdronetech.co.in</t>
         </is>
       </c>
       <c r="D170" s="11" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>Ghaziabad, India</t>
+          <t>Noida, India</t>
         </is>
       </c>
       <c r="F170" s="14" t="inlineStr">
@@ -14594,17 +14606,17 @@
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drone sprayers; drone components; lithium polymer batteries</t>
+          <t>Agricultural crop sprayers; flight automation modules; granular spreading hardware</t>
         </is>
       </c>
       <c r="K170" s="14" t="inlineStr">
         <is>
-          <t>Commercial supply of unmanned aerial vehicle accessories and power systems</t>
+          <t>B2B trading of specialized UAV components, electronics, and structural kits</t>
         </is>
       </c>
       <c r="L170" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drone sprayers, DJI battery kits, Mavic 3 Enterprise battery kits</t>
+          <t>V610P 10L Spraying Drone, Jiyi K++ V2 Flight Controller, EPS200 PRO EFT Spreader system, granular broadcasting modules</t>
         </is>
       </c>
       <c r="M170" s="11" t="inlineStr">
@@ -14612,26 +14624,14 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N170" s="14" t="inlineStr">
-        <is>
-          <t>Mr. Nonu</t>
-        </is>
-      </c>
-      <c r="O170" s="14" t="inlineStr">
-        <is>
-          <t>Proprietor</t>
-        </is>
-      </c>
+      <c r="N170" s="14" t="inlineStr"/>
+      <c r="O170" s="14" t="inlineStr"/>
       <c r="P170" s="14" t="inlineStr"/>
       <c r="Q170" s="14" t="inlineStr"/>
-      <c r="R170" s="14" t="inlineStr">
-        <is>
-          <t>08045804524</t>
-        </is>
-      </c>
+      <c r="R170" s="14" t="inlineStr"/>
       <c r="S170" s="13" t="inlineStr">
         <is>
-          <t>allaboutfly.co.in</t>
+          <t>vdronetech.co.in</t>
         </is>
       </c>
       <c r="T170" s="14" t="inlineStr"/>
@@ -14647,20 +14647,20 @@
       </c>
       <c r="B171" s="16" t="inlineStr">
         <is>
-          <t>V Drone Tech</t>
+          <t>Tradeline Corporation</t>
         </is>
       </c>
       <c r="C171" s="17" t="inlineStr">
         <is>
-          <t>vdronetech.co.in</t>
+          <t>tradelinecorp.in</t>
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="E171" s="18" t="inlineStr">
         <is>
-          <t>Noida, India</t>
+          <t>Guwahati, India</t>
         </is>
       </c>
       <c r="F171" s="18" t="inlineStr">
@@ -14675,71 +14675,91 @@
       </c>
       <c r="H171" s="18" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Family-Owned</t>
         </is>
       </c>
       <c r="I171" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-25</t>
         </is>
       </c>
       <c r="J171" s="18" t="inlineStr">
         <is>
-          <t>Agricultural crop sprayers; flight automation modules; granular spreading hardware</t>
+          <t>Battery-operated liquid sprayers; specialized crop monitoring platforms; agricultural infrastructure tools</t>
         </is>
       </c>
       <c r="K171" s="18" t="inlineStr">
         <is>
-          <t>B2B trading of specialized UAV components, electronics, and structural kits</t>
+          <t>Regional trade, hardware distribution, and technical supply of agricultural inputs in Northeast India</t>
         </is>
       </c>
       <c r="L171" s="18" t="inlineStr">
         <is>
-          <t>V610P 10L Spraying Drone, Jiyi K++ V2 Flight Controller, EPS200 PRO EFT Spreader system, granular broadcasting modules</t>
+          <t>Weather Resistant Agricultural Helicam, automated fluid spray systems</t>
         </is>
       </c>
       <c r="M171" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N171" s="18" t="inlineStr"/>
-      <c r="O171" s="18" t="inlineStr"/>
-      <c r="P171" s="18" t="inlineStr"/>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N171" s="18" t="inlineStr">
+        <is>
+          <t>Amarjyoti Sahu</t>
+        </is>
+      </c>
+      <c r="O171" s="18" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="P171" s="17" t="inlineStr">
+        <is>
+          <t>tradeline.corporation@gmail.com</t>
+        </is>
+      </c>
       <c r="Q171" s="18" t="inlineStr"/>
-      <c r="R171" s="18" t="inlineStr"/>
+      <c r="R171" s="18" t="inlineStr">
+        <is>
+          <t>+918043829381</t>
+        </is>
+      </c>
       <c r="S171" s="17" t="inlineStr">
         <is>
-          <t>vdronetech.co.in</t>
-        </is>
-      </c>
-      <c r="T171" s="18" t="inlineStr"/>
+          <t>tradelinecorp.in</t>
+        </is>
+      </c>
+      <c r="T171" s="17" t="inlineStr">
+        <is>
+          <t>tradeline.corporation@gmail.com</t>
+        </is>
+      </c>
       <c r="U171" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="46.5" customHeight="1">
+    <row r="172" ht="33" customHeight="1">
       <c r="A172" s="11" t="n">
         <v>167</v>
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t>Tradeline Corporation</t>
+          <t>The Drone Xperts</t>
         </is>
       </c>
       <c r="C172" s="13" t="inlineStr">
         <is>
-          <t>tradelinecorp.in</t>
+          <t>thedronexperts.in</t>
         </is>
       </c>
       <c r="D172" s="11" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>Guwahati, India</t>
+          <t>Agartala, India</t>
         </is>
       </c>
       <c r="F172" s="14" t="inlineStr">
@@ -14754,63 +14774,51 @@
       </c>
       <c r="H172" s="14" t="inlineStr">
         <is>
-          <t>Family-Owned</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I172" s="11" t="inlineStr">
         <is>
-          <t>11-25</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>Battery-operated liquid sprayers; specialized crop monitoring platforms; agricultural infrastructure tools</t>
+          <t>Unmanned aerial vehicles; drone components; payload sensors</t>
         </is>
       </c>
       <c r="K172" s="14" t="inlineStr">
         <is>
-          <t>Regional trade, hardware distribution, and technical supply of agricultural inputs in Northeast India</t>
+          <t>Drone distribution, maintenance, and flight training solutions</t>
         </is>
       </c>
       <c r="L172" s="14" t="inlineStr">
         <is>
-          <t>Weather Resistant Agricultural Helicam, automated fluid spray systems</t>
+          <t>DJI Mini series, DJI enterprise mapping kits, and replacement propulsion systems</t>
         </is>
       </c>
       <c r="M172" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="N172" s="14" t="inlineStr">
-        <is>
-          <t>Amarjyoti Sahu</t>
-        </is>
-      </c>
-      <c r="O172" s="14" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="P172" s="13" t="inlineStr">
-        <is>
-          <t>tradeline.corporation@gmail.com</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="N172" s="14" t="inlineStr"/>
+      <c r="O172" s="14" t="inlineStr"/>
+      <c r="P172" s="14" t="inlineStr"/>
       <c r="Q172" s="14" t="inlineStr"/>
       <c r="R172" s="14" t="inlineStr">
         <is>
-          <t>+918043829381</t>
+          <t>918415903002</t>
         </is>
       </c>
       <c r="S172" s="13" t="inlineStr">
         <is>
-          <t>tradelinecorp.in</t>
+          <t>thedronexperts.in</t>
         </is>
       </c>
       <c r="T172" s="13" t="inlineStr">
         <is>
-          <t>tradeline.corporation@gmail.com</t>
+          <t>thedronexperts@gmail.com</t>
         </is>
       </c>
       <c r="U172" s="11" t="inlineStr">
@@ -14819,26 +14827,26 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="33" customHeight="1">
+    <row r="173" ht="46.5" customHeight="1">
       <c r="A173" s="15" t="n">
         <v>168</v>
       </c>
       <c r="B173" s="16" t="inlineStr">
         <is>
-          <t>The Drone Xperts</t>
+          <t>LM and Sons</t>
         </is>
       </c>
       <c r="C173" s="17" t="inlineStr">
         <is>
-          <t>thedronexperts.in</t>
+          <t>https://www.exportersindia.com/lm-and-sons/</t>
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="E173" s="18" t="inlineStr">
         <is>
-          <t>Agartala, India</t>
+          <t>Aizawl, India</t>
         </is>
       </c>
       <c r="F173" s="18" t="inlineStr">
@@ -14863,17 +14871,17 @@
       </c>
       <c r="J173" s="18" t="inlineStr">
         <is>
-          <t>Unmanned aerial vehicles; drone components; payload sensors</t>
+          <t>Agricultural drones; aerial surveillance equipment</t>
         </is>
       </c>
       <c r="K173" s="18" t="inlineStr">
         <is>
-          <t>Drone distribution, maintenance, and flight training solutions</t>
+          <t>Supply of retail electronics, drones, and commercial supply chain solutions in Mizoram.</t>
         </is>
       </c>
       <c r="L173" s="18" t="inlineStr">
         <is>
-          <t>DJI Mini series, DJI enterprise mapping kits, and replacement propulsion systems</t>
+          <t>Agricultural spraying drones, DJI multirotor drones, battery chargers, and related drone components.</t>
         </is>
       </c>
       <c r="M173" s="15" t="inlineStr">
@@ -14885,47 +14893,39 @@
       <c r="O173" s="18" t="inlineStr"/>
       <c r="P173" s="18" t="inlineStr"/>
       <c r="Q173" s="18" t="inlineStr"/>
-      <c r="R173" s="18" t="inlineStr">
-        <is>
-          <t>918415903002</t>
-        </is>
-      </c>
+      <c r="R173" s="18" t="inlineStr"/>
       <c r="S173" s="17" t="inlineStr">
         <is>
-          <t>thedronexperts.in</t>
-        </is>
-      </c>
-      <c r="T173" s="17" t="inlineStr">
-        <is>
-          <t>thedronexperts@gmail.com</t>
-        </is>
-      </c>
+          <t>https://www.exportersindia.com/lm-and-sons/</t>
+        </is>
+      </c>
+      <c r="T173" s="18" t="inlineStr"/>
       <c r="U173" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="46.5" customHeight="1">
+    <row r="174" ht="33" customHeight="1">
       <c r="A174" s="11" t="n">
         <v>169</v>
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t>LM and Sons</t>
+          <t>GarudSpray</t>
         </is>
       </c>
       <c r="C174" s="13" t="inlineStr">
         <is>
-          <t>https://www.exportersindia.com/lm-and-sons/</t>
+          <t>garudspray.com</t>
         </is>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>Aizawl, India</t>
+          <t>Jodhpur, India</t>
         </is>
       </c>
       <c r="F174" s="14" t="inlineStr">
@@ -14950,22 +14950,22 @@
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drones; aerial surveillance equipment</t>
+          <t>Agricultural drone retail; precision spraying hardware</t>
         </is>
       </c>
       <c r="K174" s="14" t="inlineStr">
         <is>
-          <t>Supply of retail electronics, drones, and commercial supply chain solutions in Mizoram.</t>
+          <t>Distribution and downstream support of precision farming equipment in regional markets</t>
         </is>
       </c>
       <c r="L174" s="14" t="inlineStr">
         <is>
-          <t>Agricultural spraying drones, DJI multirotor drones, battery chargers, and related drone components.</t>
+          <t>Garud Agri 10, DJI Agras T25</t>
         </is>
       </c>
       <c r="M174" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N174" s="14" t="inlineStr"/>
@@ -14975,7 +14975,7 @@
       <c r="R174" s="14" t="inlineStr"/>
       <c r="S174" s="13" t="inlineStr">
         <is>
-          <t>https://www.exportersindia.com/lm-and-sons/</t>
+          <t>garudspray.com</t>
         </is>
       </c>
       <c r="T174" s="14" t="inlineStr"/>
@@ -14985,89 +14985,11 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="33" customHeight="1">
-      <c r="A175" s="15" t="n">
-        <v>170</v>
-      </c>
-      <c r="B175" s="16" t="inlineStr">
-        <is>
-          <t>GarudSpray</t>
-        </is>
-      </c>
-      <c r="C175" s="17" t="inlineStr">
-        <is>
-          <t>garudspray.com</t>
-        </is>
-      </c>
-      <c r="D175" s="15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E175" s="18" t="inlineStr">
-        <is>
-          <t>Jodhpur, India</t>
-        </is>
-      </c>
-      <c r="F175" s="18" t="inlineStr">
-        <is>
-          <t>APAC(India)</t>
-        </is>
-      </c>
-      <c r="G175" s="18" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="H175" s="18" t="inlineStr">
-        <is>
-          <t>Private Company</t>
-        </is>
-      </c>
-      <c r="I175" s="15" t="inlineStr">
-        <is>
-          <t>1-10</t>
-        </is>
-      </c>
-      <c r="J175" s="18" t="inlineStr">
-        <is>
-          <t>Agricultural drone retail; precision spraying hardware</t>
-        </is>
-      </c>
-      <c r="K175" s="18" t="inlineStr">
-        <is>
-          <t>Distribution and downstream support of precision farming equipment in regional markets</t>
-        </is>
-      </c>
-      <c r="L175" s="18" t="inlineStr">
-        <is>
-          <t>Garud Agri 10, DJI Agras T25</t>
-        </is>
-      </c>
-      <c r="M175" s="15" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="N175" s="18" t="inlineStr"/>
-      <c r="O175" s="18" t="inlineStr"/>
-      <c r="P175" s="18" t="inlineStr"/>
-      <c r="Q175" s="18" t="inlineStr"/>
-      <c r="R175" s="18" t="inlineStr"/>
-      <c r="S175" s="17" t="inlineStr">
-        <is>
-          <t>garudspray.com</t>
-        </is>
-      </c>
-      <c r="T175" s="18" t="inlineStr"/>
-      <c r="U175" s="15" t="inlineStr">
-        <is>
-          <t>+91 / IN</t>
-        </is>
-      </c>
-    </row>
+    <row r="175" ht="42" customHeight="1"/>
     <row r="176" ht="42" customHeight="1"/>
     <row r="177" ht="42" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A5:U175"/>
+  <autoFilter ref="A5:U174"/>
   <mergeCells count="4">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A4:U4"/>
@@ -15296,43 +15218,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId219"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S99" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T100" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T99" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S101" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S102" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId229"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T106" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T107" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T105" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T106" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T109" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T110" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T108" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T109" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId249"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T114" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T113" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId259"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S115" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId261"/>
@@ -15355,15 +15277,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S124" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId279"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S125" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S126" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T126" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S127" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T127" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S128" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T128" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T125" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S126" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T126" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S127" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T127" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S128" r:id="rId289"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S129" r:id="rId291"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId292"/>
@@ -15375,18 +15297,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S133" r:id="rId299"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T135" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T134" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId305"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="rId307"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T138" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T137" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId312"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId313"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId315"/>
@@ -15403,14 +15325,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId327"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T147" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T146" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId331"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T149" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T148" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId336"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId337"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId338"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId339"/>
@@ -15418,18 +15340,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId341"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId342"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P154" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T154" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P153" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T153" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId349"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId351"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T157" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T156" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId355"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId356"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId357"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId358"/>
@@ -15449,28 +15371,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId373"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P168" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P167" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId379"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId381"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId382"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId383"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P172" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T172" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T173" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P171" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T171" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T172" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId392"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId393"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S175" r:id="rId396"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
